--- a/data/calendar.xlsx
+++ b/data/calendar.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Github\Egyptian-Premier-League-Schedule-Optimizer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ibram\OneDrive\Documents\GitHub\Egyptian-Premier-League-Schedule-Optimizer\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74AB351D-5190-4077-BACE-5F4138E44255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C4A217-8486-4DDE-BA53-605B6E84E6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F713E152-EFB5-4404-AF0F-20FE5CC6E046}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F713E152-EFB5-4404-AF0F-20FE5CC6E046}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$308</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$308</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="351">
   <si>
     <t>day</t>
   </si>
@@ -1085,7 +1085,13 @@
     <t>year</t>
   </si>
   <si>
-    <t>Availabilty</t>
+    <t>Is_Ramadan</t>
+  </si>
+  <si>
+    <t>Availabilty For All</t>
+  </si>
+  <si>
+    <t>AvailabilityIfCAF</t>
   </si>
 </sst>
 </file>
@@ -1486,21 +1492,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD1ADF0-FB91-416D-8A26-8FD3BB012FA6}">
-  <dimension ref="A1:L308"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N308"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" style="3" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.88671875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15" style="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>13</v>
       </c>
@@ -1526,19 +1534,25 @@
         <v>4</v>
       </c>
       <c r="I1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="1" t="s">
         <v>348</v>
       </c>
       <c r="L1" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
@@ -1572,13 +1586,20 @@
       <c r="J2" s="9">
         <v>0</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="9">
+        <v>0</v>
+      </c>
+      <c r="L2" s="7">
+        <f>IF(SUM(H2:I2)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="7">
         <f>IF(SUM(H2:J2)&gt;0,0,1)</f>
         <v>0</v>
       </c>
-      <c r="L2" s="7"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N2" s="7"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>30</v>
       </c>
@@ -1612,13 +1633,20 @@
       <c r="J3" s="9">
         <v>0</v>
       </c>
-      <c r="K3" s="7">
-        <f t="shared" ref="K3:K66" si="3">IF(SUM(H3:J3)&gt;0,0,1)</f>
-        <v>1</v>
-      </c>
-      <c r="L3" s="7"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K3" s="9">
+        <v>0</v>
+      </c>
+      <c r="L3" s="7">
+        <f>IF(SUM(H3:I3)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M3" s="7">
+        <f t="shared" ref="M3:M66" si="3">IF(SUM(H3:J3)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="N3" s="7"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>31</v>
       </c>
@@ -1652,13 +1680,20 @@
       <c r="J4" s="9">
         <v>0</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="9">
+        <v>0</v>
+      </c>
+      <c r="L4" s="7">
+        <f>IF(SUM(H4:I4)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M4" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L4" s="7"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N4" s="7"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>32</v>
       </c>
@@ -1692,13 +1727,20 @@
       <c r="J5" s="9">
         <v>0</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="9">
+        <v>0</v>
+      </c>
+      <c r="L5" s="7">
+        <f>IF(SUM(H5:I5)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M5" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L5" s="7"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N5" s="7"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>33</v>
       </c>
@@ -1727,20 +1769,27 @@
         <v>0</v>
       </c>
       <c r="I6" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="9">
-        <v>1</v>
-      </c>
-      <c r="K6" s="7">
+        <v>0</v>
+      </c>
+      <c r="K6" s="9">
+        <v>0</v>
+      </c>
+      <c r="L6" s="7">
+        <f>IF(SUM(H6:I6)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="N6" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>35</v>
       </c>
@@ -1769,20 +1818,27 @@
         <v>0</v>
       </c>
       <c r="I7" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="9">
-        <v>1</v>
-      </c>
-      <c r="K7" s="7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="9">
+        <v>0</v>
+      </c>
+      <c r="L7" s="7">
+        <f>IF(SUM(H7:I7)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="N7" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>36</v>
       </c>
@@ -1816,13 +1872,20 @@
       <c r="J8" s="9">
         <v>0</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="9">
+        <v>0</v>
+      </c>
+      <c r="L8" s="7">
+        <f>IF(SUM(H8:I8)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M8" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L8" s="7"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N8" s="7"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>37</v>
       </c>
@@ -1856,13 +1919,20 @@
       <c r="J9" s="9">
         <v>0</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="9">
+        <v>0</v>
+      </c>
+      <c r="L9" s="7">
+        <f>IF(SUM(H9:I9)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M9" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L9" s="7"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N9" s="7"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>38</v>
       </c>
@@ -1896,13 +1966,20 @@
       <c r="J10" s="9">
         <v>0</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K10" s="9">
+        <v>0</v>
+      </c>
+      <c r="L10" s="7">
+        <f>IF(SUM(H10:I10)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M10" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L10" s="7"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N10" s="7"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>39</v>
       </c>
@@ -1936,13 +2013,20 @@
       <c r="J11" s="9">
         <v>0</v>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="9">
+        <v>0</v>
+      </c>
+      <c r="L11" s="7">
+        <f>IF(SUM(H11:I11)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M11" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L11" s="7"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N11" s="7"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>40</v>
       </c>
@@ -1976,13 +2060,20 @@
       <c r="J12" s="9">
         <v>0</v>
       </c>
-      <c r="K12" s="7">
+      <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="7">
+        <f>IF(SUM(H12:I12)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M12" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L12" s="7"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N12" s="7"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>41</v>
       </c>
@@ -2011,20 +2102,27 @@
         <v>0</v>
       </c>
       <c r="I13" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="9">
-        <v>1</v>
-      </c>
-      <c r="K13" s="7">
+        <v>0</v>
+      </c>
+      <c r="K13" s="9">
+        <v>0</v>
+      </c>
+      <c r="L13" s="7">
+        <f>IF(SUM(H13:I13)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L13" s="7" t="s">
+      <c r="N13" s="7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>43</v>
       </c>
@@ -2053,20 +2151,27 @@
         <v>0</v>
       </c>
       <c r="I14" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="9">
-        <v>1</v>
-      </c>
-      <c r="K14" s="7">
+        <v>0</v>
+      </c>
+      <c r="K14" s="9">
+        <v>0</v>
+      </c>
+      <c r="L14" s="7">
+        <f>IF(SUM(H14:I14)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L14" s="7" t="s">
+      <c r="N14" s="7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>44</v>
       </c>
@@ -2100,13 +2205,20 @@
       <c r="J15" s="9">
         <v>0</v>
       </c>
-      <c r="K15" s="7">
+      <c r="K15" s="9">
+        <v>0</v>
+      </c>
+      <c r="L15" s="7">
+        <f>IF(SUM(H15:I15)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M15" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L15" s="7"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N15" s="7"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>45</v>
       </c>
@@ -2140,13 +2252,20 @@
       <c r="J16" s="9">
         <v>0</v>
       </c>
-      <c r="K16" s="7">
+      <c r="K16" s="9">
+        <v>0</v>
+      </c>
+      <c r="L16" s="7">
+        <f>IF(SUM(H16:I16)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M16" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L16" s="7"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N16" s="7"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>46</v>
       </c>
@@ -2180,13 +2299,20 @@
       <c r="J17" s="9">
         <v>0</v>
       </c>
-      <c r="K17" s="7">
+      <c r="K17" s="9">
+        <v>0</v>
+      </c>
+      <c r="L17" s="7">
+        <f>IF(SUM(H17:I17)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M17" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L17" s="7"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N17" s="7"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>47</v>
       </c>
@@ -2220,13 +2346,20 @@
       <c r="J18" s="9">
         <v>0</v>
       </c>
-      <c r="K18" s="7">
+      <c r="K18" s="9">
+        <v>0</v>
+      </c>
+      <c r="L18" s="7">
+        <f>IF(SUM(H18:I18)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M18" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L18" s="7"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N18" s="7"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>48</v>
       </c>
@@ -2260,13 +2393,20 @@
       <c r="J19" s="9">
         <v>0</v>
       </c>
-      <c r="K19" s="7">
+      <c r="K19" s="9">
+        <v>0</v>
+      </c>
+      <c r="L19" s="7">
+        <f>IF(SUM(H19:I19)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M19" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L19" s="7"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N19" s="7"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>49</v>
       </c>
@@ -2295,20 +2435,27 @@
         <v>0</v>
       </c>
       <c r="I20" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="9">
-        <v>1</v>
-      </c>
-      <c r="K20" s="7">
+        <v>0</v>
+      </c>
+      <c r="K20" s="9">
+        <v>0</v>
+      </c>
+      <c r="L20" s="7">
+        <f>IF(SUM(H20:I20)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L20" s="7" t="s">
+      <c r="N20" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>51</v>
       </c>
@@ -2337,20 +2484,27 @@
         <v>0</v>
       </c>
       <c r="I21" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="9">
-        <v>1</v>
-      </c>
-      <c r="K21" s="7">
+        <v>0</v>
+      </c>
+      <c r="K21" s="9">
+        <v>0</v>
+      </c>
+      <c r="L21" s="7">
+        <f>IF(SUM(H21:I21)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M21" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L21" s="7" t="s">
+      <c r="N21" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>52</v>
       </c>
@@ -2384,13 +2538,20 @@
       <c r="J22" s="9">
         <v>0</v>
       </c>
-      <c r="K22" s="7">
+      <c r="K22" s="9">
+        <v>0</v>
+      </c>
+      <c r="L22" s="7">
+        <f>IF(SUM(H22:I22)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M22" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L22" s="7"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N22" s="7"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>53</v>
       </c>
@@ -2424,13 +2585,20 @@
       <c r="J23" s="9">
         <v>0</v>
       </c>
-      <c r="K23" s="7">
+      <c r="K23" s="9">
+        <v>0</v>
+      </c>
+      <c r="L23" s="7">
+        <f>IF(SUM(H23:I23)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M23" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L23" s="7"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N23" s="7"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>54</v>
       </c>
@@ -2464,13 +2632,20 @@
       <c r="J24" s="9">
         <v>0</v>
       </c>
-      <c r="K24" s="7">
+      <c r="K24" s="9">
+        <v>0</v>
+      </c>
+      <c r="L24" s="7">
+        <f>IF(SUM(H24:I24)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M24" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L24" s="7"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N24" s="7"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>55</v>
       </c>
@@ -2504,13 +2679,20 @@
       <c r="J25" s="9">
         <v>0</v>
       </c>
-      <c r="K25" s="7">
+      <c r="K25" s="9">
+        <v>0</v>
+      </c>
+      <c r="L25" s="7">
+        <f>IF(SUM(H25:I25)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M25" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L25" s="7"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N25" s="7"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>56</v>
       </c>
@@ -2544,15 +2726,22 @@
       <c r="J26" s="9">
         <v>0</v>
       </c>
-      <c r="K26" s="7">
+      <c r="K26" s="9">
+        <v>0</v>
+      </c>
+      <c r="L26" s="7">
+        <f>IF(SUM(H26:I26)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L26" s="7" t="s">
+      <c r="N26" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>57</v>
       </c>
@@ -2586,15 +2775,22 @@
       <c r="J27" s="9">
         <v>0</v>
       </c>
-      <c r="K27" s="7">
+      <c r="K27" s="9">
+        <v>0</v>
+      </c>
+      <c r="L27" s="7">
+        <f>IF(SUM(H27:I27)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L27" s="7" t="s">
+      <c r="N27" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>58</v>
       </c>
@@ -2628,15 +2824,22 @@
       <c r="J28" s="9">
         <v>0</v>
       </c>
-      <c r="K28" s="7">
+      <c r="K28" s="9">
+        <v>0</v>
+      </c>
+      <c r="L28" s="7">
+        <f>IF(SUM(H28:I28)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M28" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L28" s="7" t="s">
+      <c r="N28" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>59</v>
       </c>
@@ -2670,15 +2873,22 @@
       <c r="J29" s="9">
         <v>0</v>
       </c>
-      <c r="K29" s="7">
+      <c r="K29" s="9">
+        <v>0</v>
+      </c>
+      <c r="L29" s="7">
+        <f>IF(SUM(H29:I29)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L29" s="7" t="s">
+      <c r="N29" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>60</v>
       </c>
@@ -2712,15 +2922,22 @@
       <c r="J30" s="9">
         <v>0</v>
       </c>
-      <c r="K30" s="7">
+      <c r="K30" s="9">
+        <v>0</v>
+      </c>
+      <c r="L30" s="7">
+        <f>IF(SUM(H30:I30)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L30" s="7" t="s">
+      <c r="N30" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>61</v>
       </c>
@@ -2754,15 +2971,22 @@
       <c r="J31" s="9">
         <v>0</v>
       </c>
-      <c r="K31" s="7">
+      <c r="K31" s="9">
+        <v>0</v>
+      </c>
+      <c r="L31" s="7">
+        <f>IF(SUM(H31:I31)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L31" s="7" t="s">
+      <c r="N31" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>62</v>
       </c>
@@ -2796,15 +3020,22 @@
       <c r="J32" s="9">
         <v>0</v>
       </c>
-      <c r="K32" s="7">
+      <c r="K32" s="9">
+        <v>0</v>
+      </c>
+      <c r="L32" s="7">
+        <f>IF(SUM(H32:I32)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M32" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L32" s="7" t="s">
+      <c r="N32" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>63</v>
       </c>
@@ -2838,15 +3069,22 @@
       <c r="J33" s="9">
         <v>0</v>
       </c>
-      <c r="K33" s="7">
+      <c r="K33" s="9">
+        <v>0</v>
+      </c>
+      <c r="L33" s="7">
+        <f>IF(SUM(H33:I33)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M33" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L33" s="7" t="s">
+      <c r="N33" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>64</v>
       </c>
@@ -2880,13 +3118,20 @@
       <c r="J34" s="9">
         <v>0</v>
       </c>
-      <c r="K34" s="7">
+      <c r="K34" s="9">
+        <v>0</v>
+      </c>
+      <c r="L34" s="7">
+        <f>IF(SUM(H34:I34)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M34" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L34" s="7"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N34" s="7"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>65</v>
       </c>
@@ -2920,13 +3165,20 @@
       <c r="J35" s="9">
         <v>0</v>
       </c>
-      <c r="K35" s="7">
+      <c r="K35" s="9">
+        <v>0</v>
+      </c>
+      <c r="L35" s="7">
+        <f>IF(SUM(H35:I35)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M35" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L35" s="7"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N35" s="7"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>66</v>
       </c>
@@ -2960,13 +3212,20 @@
       <c r="J36" s="9">
         <v>0</v>
       </c>
-      <c r="K36" s="7">
+      <c r="K36" s="9">
+        <v>0</v>
+      </c>
+      <c r="L36" s="7">
+        <f>IF(SUM(H36:I36)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M36" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L36" s="7"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N36" s="7"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>67</v>
       </c>
@@ -3000,13 +3259,20 @@
       <c r="J37" s="9">
         <v>0</v>
       </c>
-      <c r="K37" s="7">
+      <c r="K37" s="9">
+        <v>0</v>
+      </c>
+      <c r="L37" s="7">
+        <f>IF(SUM(H37:I37)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M37" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L37" s="7"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N37" s="7"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>68</v>
       </c>
@@ -3040,13 +3306,20 @@
       <c r="J38" s="9">
         <v>0</v>
       </c>
-      <c r="K38" s="7">
+      <c r="K38" s="9">
+        <v>0</v>
+      </c>
+      <c r="L38" s="7">
+        <f>IF(SUM(H38:I38)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M38" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L38" s="7"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N38" s="7"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>69</v>
       </c>
@@ -3080,13 +3353,20 @@
       <c r="J39" s="9">
         <v>0</v>
       </c>
-      <c r="K39" s="7">
+      <c r="K39" s="9">
+        <v>0</v>
+      </c>
+      <c r="L39" s="7">
+        <f>IF(SUM(H39:I39)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M39" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L39" s="7"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N39" s="7"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>70</v>
       </c>
@@ -3120,13 +3400,20 @@
       <c r="J40" s="9">
         <v>0</v>
       </c>
-      <c r="K40" s="7">
+      <c r="K40" s="9">
+        <v>0</v>
+      </c>
+      <c r="L40" s="7">
+        <f>IF(SUM(H40:I40)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M40" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L40" s="7"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N40" s="7"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>71</v>
       </c>
@@ -3155,20 +3442,27 @@
         <v>0</v>
       </c>
       <c r="I41" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" s="9">
-        <v>0</v>
-      </c>
-      <c r="K41" s="7">
+        <v>1</v>
+      </c>
+      <c r="K41" s="9">
+        <v>0</v>
+      </c>
+      <c r="L41" s="7">
+        <f>IF(SUM(H41:I41)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M41" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L41" s="7" t="s">
+      <c r="N41" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>72</v>
       </c>
@@ -3197,20 +3491,27 @@
         <v>0</v>
       </c>
       <c r="I42" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="9">
-        <v>0</v>
-      </c>
-      <c r="K42" s="7">
+        <v>1</v>
+      </c>
+      <c r="K42" s="9">
+        <v>0</v>
+      </c>
+      <c r="L42" s="7">
+        <f>IF(SUM(H42:I42)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M42" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L42" s="7" t="s">
+      <c r="N42" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>73</v>
       </c>
@@ -3244,13 +3545,20 @@
       <c r="J43" s="9">
         <v>0</v>
       </c>
-      <c r="K43" s="7">
+      <c r="K43" s="9">
+        <v>0</v>
+      </c>
+      <c r="L43" s="7">
+        <f>IF(SUM(H43:I43)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M43" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L43" s="7"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N43" s="7"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>74</v>
       </c>
@@ -3284,13 +3592,20 @@
       <c r="J44" s="9">
         <v>0</v>
       </c>
-      <c r="K44" s="7">
+      <c r="K44" s="9">
+        <v>0</v>
+      </c>
+      <c r="L44" s="7">
+        <f>IF(SUM(H44:I44)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M44" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L44" s="7"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N44" s="7"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>75</v>
       </c>
@@ -3324,13 +3639,20 @@
       <c r="J45" s="9">
         <v>0</v>
       </c>
-      <c r="K45" s="7">
+      <c r="K45" s="9">
+        <v>0</v>
+      </c>
+      <c r="L45" s="7">
+        <f>IF(SUM(H45:I45)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M45" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L45" s="7"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N45" s="7"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>76</v>
       </c>
@@ -3364,13 +3686,20 @@
       <c r="J46" s="9">
         <v>0</v>
       </c>
-      <c r="K46" s="7">
+      <c r="K46" s="9">
+        <v>0</v>
+      </c>
+      <c r="L46" s="7">
+        <f>IF(SUM(H46:I46)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M46" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L46" s="7"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N46" s="7"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>77</v>
       </c>
@@ -3404,13 +3733,20 @@
       <c r="J47" s="9">
         <v>0</v>
       </c>
-      <c r="K47" s="7">
+      <c r="K47" s="9">
+        <v>0</v>
+      </c>
+      <c r="L47" s="7">
+        <f>IF(SUM(H47:I47)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M47" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L47" s="7"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N47" s="7"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>78</v>
       </c>
@@ -3439,20 +3775,27 @@
         <v>0</v>
       </c>
       <c r="I48" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="9">
-        <v>1</v>
-      </c>
-      <c r="K48" s="7">
+        <v>0</v>
+      </c>
+      <c r="K48" s="9">
+        <v>0</v>
+      </c>
+      <c r="L48" s="7">
+        <f>IF(SUM(H48:I48)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M48" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L48" s="7" t="s">
+      <c r="N48" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>80</v>
       </c>
@@ -3481,20 +3824,27 @@
         <v>0</v>
       </c>
       <c r="I49" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="9">
-        <v>1</v>
-      </c>
-      <c r="K49" s="7">
+        <v>0</v>
+      </c>
+      <c r="K49" s="9">
+        <v>0</v>
+      </c>
+      <c r="L49" s="7">
+        <f>IF(SUM(H49:I49)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M49" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L49" s="7" t="s">
+      <c r="N49" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>81</v>
       </c>
@@ -3528,13 +3878,20 @@
       <c r="J50" s="9">
         <v>0</v>
       </c>
-      <c r="K50" s="7">
+      <c r="K50" s="9">
+        <v>0</v>
+      </c>
+      <c r="L50" s="7">
+        <f>IF(SUM(H50:I50)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M50" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L50" s="7"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N50" s="7"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>82</v>
       </c>
@@ -3568,13 +3925,20 @@
       <c r="J51" s="9">
         <v>0</v>
       </c>
-      <c r="K51" s="7">
+      <c r="K51" s="9">
+        <v>0</v>
+      </c>
+      <c r="L51" s="7">
+        <f>IF(SUM(H51:I51)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M51" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L51" s="7"/>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N51" s="7"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>83</v>
       </c>
@@ -3608,13 +3972,20 @@
       <c r="J52" s="9">
         <v>0</v>
       </c>
-      <c r="K52" s="7">
+      <c r="K52" s="9">
+        <v>0</v>
+      </c>
+      <c r="L52" s="7">
+        <f>IF(SUM(H52:I52)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M52" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L52" s="7"/>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N52" s="7"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>84</v>
       </c>
@@ -3648,13 +4019,20 @@
       <c r="J53" s="9">
         <v>0</v>
       </c>
-      <c r="K53" s="7">
+      <c r="K53" s="9">
+        <v>0</v>
+      </c>
+      <c r="L53" s="7">
+        <f>IF(SUM(H53:I53)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M53" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L53" s="7"/>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N53" s="7"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>85</v>
       </c>
@@ -3688,13 +4066,20 @@
       <c r="J54" s="9">
         <v>0</v>
       </c>
-      <c r="K54" s="7">
+      <c r="K54" s="9">
+        <v>0</v>
+      </c>
+      <c r="L54" s="7">
+        <f>IF(SUM(H54:I54)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M54" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L54" s="7"/>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N54" s="7"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>86</v>
       </c>
@@ -3723,20 +4108,27 @@
         <v>0</v>
       </c>
       <c r="I55" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" s="9">
-        <v>0</v>
-      </c>
-      <c r="K55" s="7">
+        <v>1</v>
+      </c>
+      <c r="K55" s="9">
+        <v>0</v>
+      </c>
+      <c r="L55" s="7">
+        <f>IF(SUM(H55:I55)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M55" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L55" s="7" t="s">
+      <c r="N55" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>87</v>
       </c>
@@ -3765,20 +4157,27 @@
         <v>0</v>
       </c>
       <c r="I56" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" s="9">
-        <v>0</v>
-      </c>
-      <c r="K56" s="7">
+        <v>1</v>
+      </c>
+      <c r="K56" s="9">
+        <v>0</v>
+      </c>
+      <c r="L56" s="7">
+        <f>IF(SUM(H56:I56)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M56" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L56" s="7" t="s">
+      <c r="N56" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>88</v>
       </c>
@@ -3812,13 +4211,20 @@
       <c r="J57" s="9">
         <v>0</v>
       </c>
-      <c r="K57" s="7">
+      <c r="K57" s="9">
+        <v>0</v>
+      </c>
+      <c r="L57" s="7">
+        <f>IF(SUM(H57:I57)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M57" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L57" s="7"/>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N57" s="7"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>89</v>
       </c>
@@ -3852,13 +4258,20 @@
       <c r="J58" s="9">
         <v>0</v>
       </c>
-      <c r="K58" s="7">
+      <c r="K58" s="9">
+        <v>0</v>
+      </c>
+      <c r="L58" s="7">
+        <f>IF(SUM(H58:I58)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M58" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L58" s="7"/>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N58" s="7"/>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>90</v>
       </c>
@@ -3892,13 +4305,20 @@
       <c r="J59" s="9">
         <v>0</v>
       </c>
-      <c r="K59" s="7">
+      <c r="K59" s="9">
+        <v>0</v>
+      </c>
+      <c r="L59" s="7">
+        <f>IF(SUM(H59:I59)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M59" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L59" s="7"/>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N59" s="7"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>91</v>
       </c>
@@ -3932,13 +4352,20 @@
       <c r="J60" s="9">
         <v>0</v>
       </c>
-      <c r="K60" s="7">
+      <c r="K60" s="9">
+        <v>0</v>
+      </c>
+      <c r="L60" s="7">
+        <f>IF(SUM(H60:I60)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M60" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L60" s="7"/>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N60" s="7"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>92</v>
       </c>
@@ -3972,13 +4399,20 @@
       <c r="J61" s="9">
         <v>0</v>
       </c>
-      <c r="K61" s="7">
+      <c r="K61" s="9">
+        <v>0</v>
+      </c>
+      <c r="L61" s="7">
+        <f>IF(SUM(H61:I61)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M61" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L61" s="7"/>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N61" s="7"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>93</v>
       </c>
@@ -4012,15 +4446,22 @@
       <c r="J62" s="9">
         <v>0</v>
       </c>
-      <c r="K62" s="7">
+      <c r="K62" s="9">
+        <v>0</v>
+      </c>
+      <c r="L62" s="7">
+        <f>IF(SUM(H62:I62)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M62" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L62" s="7" t="s">
+      <c r="N62" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>94</v>
       </c>
@@ -4054,15 +4495,22 @@
       <c r="J63" s="9">
         <v>0</v>
       </c>
-      <c r="K63" s="7">
+      <c r="K63" s="9">
+        <v>0</v>
+      </c>
+      <c r="L63" s="7">
+        <f>IF(SUM(H63:I63)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M63" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L63" s="7" t="s">
+      <c r="N63" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>95</v>
       </c>
@@ -4096,15 +4544,22 @@
       <c r="J64" s="9">
         <v>0</v>
       </c>
-      <c r="K64" s="7">
+      <c r="K64" s="9">
+        <v>0</v>
+      </c>
+      <c r="L64" s="7">
+        <f>IF(SUM(H64:I64)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M64" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L64" s="7" t="s">
+      <c r="N64" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>96</v>
       </c>
@@ -4138,15 +4593,22 @@
       <c r="J65" s="9">
         <v>0</v>
       </c>
-      <c r="K65" s="7">
+      <c r="K65" s="9">
+        <v>0</v>
+      </c>
+      <c r="L65" s="7">
+        <f>IF(SUM(H65:I65)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M65" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L65" s="7" t="s">
+      <c r="N65" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>97</v>
       </c>
@@ -4180,15 +4642,22 @@
       <c r="J66" s="9">
         <v>0</v>
       </c>
-      <c r="K66" s="7">
+      <c r="K66" s="9">
+        <v>0</v>
+      </c>
+      <c r="L66" s="7">
+        <f>IF(SUM(H66:I66)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M66" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L66" s="7" t="s">
+      <c r="N66" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>98</v>
       </c>
@@ -4222,15 +4691,22 @@
       <c r="J67" s="9">
         <v>0</v>
       </c>
-      <c r="K67" s="7">
-        <f t="shared" ref="K67:K130" si="7">IF(SUM(H67:J67)&gt;0,0,1)</f>
-        <v>0</v>
-      </c>
-      <c r="L67" s="7" t="s">
+      <c r="K67" s="9">
+        <v>0</v>
+      </c>
+      <c r="L67" s="7">
+        <f>IF(SUM(H67:I67)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M67" s="7">
+        <f t="shared" ref="M67:M130" si="7">IF(SUM(H67:J67)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="N67" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>99</v>
       </c>
@@ -4264,15 +4740,22 @@
       <c r="J68" s="9">
         <v>0</v>
       </c>
-      <c r="K68" s="7">
+      <c r="K68" s="9">
+        <v>0</v>
+      </c>
+      <c r="L68" s="7">
+        <f>IF(SUM(H68:I68)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M68" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L68" s="7" t="s">
+      <c r="N68" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>100</v>
       </c>
@@ -4306,15 +4789,22 @@
       <c r="J69" s="9">
         <v>0</v>
       </c>
-      <c r="K69" s="7">
+      <c r="K69" s="9">
+        <v>0</v>
+      </c>
+      <c r="L69" s="7">
+        <f>IF(SUM(H69:I69)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M69" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L69" s="7" t="s">
+      <c r="N69" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>101</v>
       </c>
@@ -4348,13 +4838,20 @@
       <c r="J70" s="9">
         <v>0</v>
       </c>
-      <c r="K70" s="7">
+      <c r="K70" s="9">
+        <v>0</v>
+      </c>
+      <c r="L70" s="7">
+        <f>IF(SUM(H70:I70)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M70" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L70" s="7"/>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N70" s="7"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>102</v>
       </c>
@@ -4388,13 +4885,20 @@
       <c r="J71" s="9">
         <v>0</v>
       </c>
-      <c r="K71" s="7">
+      <c r="K71" s="9">
+        <v>0</v>
+      </c>
+      <c r="L71" s="7">
+        <f>IF(SUM(H71:I71)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M71" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L71" s="7"/>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N71" s="7"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>103</v>
       </c>
@@ -4428,13 +4932,20 @@
       <c r="J72" s="9">
         <v>0</v>
       </c>
-      <c r="K72" s="7">
+      <c r="K72" s="9">
+        <v>0</v>
+      </c>
+      <c r="L72" s="7">
+        <f>IF(SUM(H72:I72)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M72" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L72" s="7"/>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N72" s="7"/>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>104</v>
       </c>
@@ -4468,13 +4979,20 @@
       <c r="J73" s="9">
         <v>0</v>
       </c>
-      <c r="K73" s="7">
+      <c r="K73" s="9">
+        <v>0</v>
+      </c>
+      <c r="L73" s="7">
+        <f>IF(SUM(H73:I73)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M73" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L73" s="7"/>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N73" s="7"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>105</v>
       </c>
@@ -4508,13 +5026,20 @@
       <c r="J74" s="9">
         <v>0</v>
       </c>
-      <c r="K74" s="7">
+      <c r="K74" s="9">
+        <v>0</v>
+      </c>
+      <c r="L74" s="7">
+        <f>IF(SUM(H74:I74)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M74" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L74" s="7"/>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N74" s="7"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>106</v>
       </c>
@@ -4548,13 +5073,20 @@
       <c r="J75" s="9">
         <v>0</v>
       </c>
-      <c r="K75" s="7">
+      <c r="K75" s="9">
+        <v>0</v>
+      </c>
+      <c r="L75" s="7">
+        <f>IF(SUM(H75:I75)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M75" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L75" s="7"/>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N75" s="7"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>107</v>
       </c>
@@ -4583,20 +5115,27 @@
         <v>0</v>
       </c>
       <c r="I76" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" s="9">
-        <v>1</v>
-      </c>
-      <c r="K76" s="7">
+        <v>0</v>
+      </c>
+      <c r="K76" s="9">
+        <v>0</v>
+      </c>
+      <c r="L76" s="7">
+        <f>IF(SUM(H76:I76)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M76" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L76" s="7" t="s">
+      <c r="N76" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>109</v>
       </c>
@@ -4625,20 +5164,27 @@
         <v>0</v>
       </c>
       <c r="I77" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" s="9">
-        <v>1</v>
-      </c>
-      <c r="K77" s="7">
+        <v>0</v>
+      </c>
+      <c r="K77" s="9">
+        <v>0</v>
+      </c>
+      <c r="L77" s="7">
+        <f>IF(SUM(H77:I77)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M77" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L77" s="7" t="s">
+      <c r="N77" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>110</v>
       </c>
@@ -4672,13 +5218,20 @@
       <c r="J78" s="9">
         <v>0</v>
       </c>
-      <c r="K78" s="7">
+      <c r="K78" s="9">
+        <v>0</v>
+      </c>
+      <c r="L78" s="7">
+        <f>IF(SUM(H78:I78)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M78" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L78" s="7"/>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N78" s="7"/>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>111</v>
       </c>
@@ -4712,13 +5265,20 @@
       <c r="J79" s="9">
         <v>0</v>
       </c>
-      <c r="K79" s="7">
+      <c r="K79" s="9">
+        <v>0</v>
+      </c>
+      <c r="L79" s="7">
+        <f>IF(SUM(H79:I79)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M79" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L79" s="7"/>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N79" s="7"/>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>112</v>
       </c>
@@ -4752,13 +5312,20 @@
       <c r="J80" s="9">
         <v>0</v>
       </c>
-      <c r="K80" s="7">
+      <c r="K80" s="9">
+        <v>0</v>
+      </c>
+      <c r="L80" s="7">
+        <f>IF(SUM(H80:I80)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M80" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L80" s="7"/>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N80" s="7"/>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>113</v>
       </c>
@@ -4792,13 +5359,20 @@
       <c r="J81" s="9">
         <v>0</v>
       </c>
-      <c r="K81" s="7">
+      <c r="K81" s="9">
+        <v>0</v>
+      </c>
+      <c r="L81" s="7">
+        <f>IF(SUM(H81:I81)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M81" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L81" s="7"/>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N81" s="7"/>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>114</v>
       </c>
@@ -4832,13 +5406,20 @@
       <c r="J82" s="9">
         <v>0</v>
       </c>
-      <c r="K82" s="7">
+      <c r="K82" s="9">
+        <v>0</v>
+      </c>
+      <c r="L82" s="7">
+        <f>IF(SUM(H82:I82)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M82" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L82" s="7"/>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N82" s="7"/>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>115</v>
       </c>
@@ -4867,20 +5448,27 @@
         <v>0</v>
       </c>
       <c r="I83" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J83" s="9">
-        <v>0</v>
-      </c>
-      <c r="K83" s="7">
+        <v>1</v>
+      </c>
+      <c r="K83" s="9">
+        <v>0</v>
+      </c>
+      <c r="L83" s="7">
+        <f>IF(SUM(H83:I83)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M83" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L83" s="7" t="s">
+      <c r="N83" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>116</v>
       </c>
@@ -4909,20 +5497,27 @@
         <v>0</v>
       </c>
       <c r="I84" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J84" s="9">
-        <v>0</v>
-      </c>
-      <c r="K84" s="7">
+        <v>1</v>
+      </c>
+      <c r="K84" s="9">
+        <v>0</v>
+      </c>
+      <c r="L84" s="7">
+        <f>IF(SUM(H84:I84)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M84" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L84" s="7" t="s">
+      <c r="N84" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>117</v>
       </c>
@@ -4956,13 +5551,20 @@
       <c r="J85" s="9">
         <v>0</v>
       </c>
-      <c r="K85" s="7">
+      <c r="K85" s="9">
+        <v>0</v>
+      </c>
+      <c r="L85" s="7">
+        <f>IF(SUM(H85:I85)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M85" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L85" s="7"/>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N85" s="7"/>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>118</v>
       </c>
@@ -4996,13 +5598,20 @@
       <c r="J86" s="9">
         <v>0</v>
       </c>
-      <c r="K86" s="7">
+      <c r="K86" s="9">
+        <v>0</v>
+      </c>
+      <c r="L86" s="7">
+        <f>IF(SUM(H86:I86)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M86" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L86" s="7"/>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N86" s="7"/>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>119</v>
       </c>
@@ -5036,13 +5645,20 @@
       <c r="J87" s="9">
         <v>0</v>
       </c>
-      <c r="K87" s="7">
+      <c r="K87" s="9">
+        <v>0</v>
+      </c>
+      <c r="L87" s="7">
+        <f>IF(SUM(H87:I87)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M87" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L87" s="7"/>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N87" s="7"/>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>120</v>
       </c>
@@ -5076,13 +5692,20 @@
       <c r="J88" s="9">
         <v>0</v>
       </c>
-      <c r="K88" s="7">
+      <c r="K88" s="9">
+        <v>0</v>
+      </c>
+      <c r="L88" s="7">
+        <f>IF(SUM(H88:I88)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M88" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L88" s="7"/>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N88" s="7"/>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>121</v>
       </c>
@@ -5116,13 +5739,20 @@
       <c r="J89" s="9">
         <v>0</v>
       </c>
-      <c r="K89" s="7">
+      <c r="K89" s="9">
+        <v>0</v>
+      </c>
+      <c r="L89" s="7">
+        <f>IF(SUM(H89:I89)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M89" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L89" s="7"/>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N89" s="7"/>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>122</v>
       </c>
@@ -5151,20 +5781,27 @@
         <v>0</v>
       </c>
       <c r="I90" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" s="9">
-        <v>1</v>
-      </c>
-      <c r="K90" s="7">
+        <v>0</v>
+      </c>
+      <c r="K90" s="9">
+        <v>0</v>
+      </c>
+      <c r="L90" s="7">
+        <f>IF(SUM(H90:I90)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M90" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L90" s="7" t="s">
+      <c r="N90" s="7" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>124</v>
       </c>
@@ -5193,20 +5830,27 @@
         <v>0</v>
       </c>
       <c r="I91" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" s="9">
-        <v>1</v>
-      </c>
-      <c r="K91" s="7">
+        <v>0</v>
+      </c>
+      <c r="K91" s="9">
+        <v>0</v>
+      </c>
+      <c r="L91" s="7">
+        <f>IF(SUM(H91:I91)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M91" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L91" s="7" t="s">
+      <c r="N91" s="7" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>125</v>
       </c>
@@ -5240,13 +5884,20 @@
       <c r="J92" s="9">
         <v>0</v>
       </c>
-      <c r="K92" s="7">
+      <c r="K92" s="9">
+        <v>0</v>
+      </c>
+      <c r="L92" s="7">
+        <f>IF(SUM(H92:I92)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M92" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L92" s="7"/>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N92" s="7"/>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>126</v>
       </c>
@@ -5280,13 +5931,20 @@
       <c r="J93" s="9">
         <v>0</v>
       </c>
-      <c r="K93" s="7">
+      <c r="K93" s="9">
+        <v>0</v>
+      </c>
+      <c r="L93" s="7">
+        <f>IF(SUM(H93:I93)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M93" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L93" s="7"/>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N93" s="7"/>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>127</v>
       </c>
@@ -5320,13 +5978,20 @@
       <c r="J94" s="9">
         <v>0</v>
       </c>
-      <c r="K94" s="7">
+      <c r="K94" s="9">
+        <v>0</v>
+      </c>
+      <c r="L94" s="7">
+        <f>IF(SUM(H94:I94)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M94" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L94" s="7"/>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N94" s="7"/>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>128</v>
       </c>
@@ -5360,13 +6025,20 @@
       <c r="J95" s="9">
         <v>0</v>
       </c>
-      <c r="K95" s="7">
+      <c r="K95" s="9">
+        <v>0</v>
+      </c>
+      <c r="L95" s="7">
+        <f>IF(SUM(H95:I95)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M95" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L95" s="7"/>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N95" s="7"/>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>129</v>
       </c>
@@ -5400,13 +6072,20 @@
       <c r="J96" s="9">
         <v>0</v>
       </c>
-      <c r="K96" s="7">
+      <c r="K96" s="9">
+        <v>0</v>
+      </c>
+      <c r="L96" s="7">
+        <f>IF(SUM(H96:I96)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M96" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L96" s="7"/>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N96" s="7"/>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>130</v>
       </c>
@@ -5440,15 +6119,22 @@
       <c r="J97" s="9">
         <v>0</v>
       </c>
-      <c r="K97" s="7">
+      <c r="K97" s="9">
+        <v>0</v>
+      </c>
+      <c r="L97" s="7">
+        <f>IF(SUM(H97:I97)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M97" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L97" s="7" t="s">
+      <c r="N97" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>131</v>
       </c>
@@ -5482,15 +6168,22 @@
       <c r="J98" s="9">
         <v>0</v>
       </c>
-      <c r="K98" s="7">
+      <c r="K98" s="9">
+        <v>0</v>
+      </c>
+      <c r="L98" s="7">
+        <f>IF(SUM(H98:I98)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M98" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L98" s="7" t="s">
+      <c r="N98" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>132</v>
       </c>
@@ -5524,15 +6217,22 @@
       <c r="J99" s="9">
         <v>0</v>
       </c>
-      <c r="K99" s="7">
+      <c r="K99" s="9">
+        <v>0</v>
+      </c>
+      <c r="L99" s="7">
+        <f>IF(SUM(H99:I99)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M99" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L99" s="7" t="s">
+      <c r="N99" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>133</v>
       </c>
@@ -5566,15 +6266,22 @@
       <c r="J100" s="9">
         <v>0</v>
       </c>
-      <c r="K100" s="7">
+      <c r="K100" s="9">
+        <v>0</v>
+      </c>
+      <c r="L100" s="7">
+        <f>IF(SUM(H100:I100)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M100" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L100" s="7" t="s">
+      <c r="N100" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>134</v>
       </c>
@@ -5608,15 +6315,22 @@
       <c r="J101" s="9">
         <v>0</v>
       </c>
-      <c r="K101" s="7">
+      <c r="K101" s="9">
+        <v>0</v>
+      </c>
+      <c r="L101" s="7">
+        <f>IF(SUM(H101:I101)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M101" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L101" s="7" t="s">
+      <c r="N101" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>135</v>
       </c>
@@ -5650,15 +6364,22 @@
       <c r="J102" s="9">
         <v>0</v>
       </c>
-      <c r="K102" s="7">
+      <c r="K102" s="9">
+        <v>0</v>
+      </c>
+      <c r="L102" s="7">
+        <f>IF(SUM(H102:I102)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M102" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L102" s="7" t="s">
+      <c r="N102" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>136</v>
       </c>
@@ -5692,15 +6413,22 @@
       <c r="J103" s="9">
         <v>0</v>
       </c>
-      <c r="K103" s="7">
+      <c r="K103" s="9">
+        <v>0</v>
+      </c>
+      <c r="L103" s="7">
+        <f>IF(SUM(H103:I103)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M103" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L103" s="7" t="s">
+      <c r="N103" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>137</v>
       </c>
@@ -5734,15 +6462,22 @@
       <c r="J104" s="9">
         <v>0</v>
       </c>
-      <c r="K104" s="7">
+      <c r="K104" s="9">
+        <v>0</v>
+      </c>
+      <c r="L104" s="7">
+        <f>IF(SUM(H104:I104)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M104" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L104" s="7" t="s">
+      <c r="N104" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>138</v>
       </c>
@@ -5776,13 +6511,20 @@
       <c r="J105" s="9">
         <v>0</v>
       </c>
-      <c r="K105" s="7">
+      <c r="K105" s="9">
+        <v>0</v>
+      </c>
+      <c r="L105" s="7">
+        <f>IF(SUM(H105:I105)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M105" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L105" s="7"/>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N105" s="7"/>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>139</v>
       </c>
@@ -5816,13 +6558,20 @@
       <c r="J106" s="9">
         <v>0</v>
       </c>
-      <c r="K106" s="7">
+      <c r="K106" s="9">
+        <v>0</v>
+      </c>
+      <c r="L106" s="7">
+        <f>IF(SUM(H106:I106)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M106" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L106" s="7"/>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N106" s="7"/>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>140</v>
       </c>
@@ -5856,13 +6605,20 @@
       <c r="J107" s="9">
         <v>0</v>
       </c>
-      <c r="K107" s="7">
+      <c r="K107" s="9">
+        <v>0</v>
+      </c>
+      <c r="L107" s="7">
+        <f>IF(SUM(H107:I107)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M107" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L107" s="7"/>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N107" s="7"/>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>141</v>
       </c>
@@ -5896,13 +6652,20 @@
       <c r="J108" s="9">
         <v>0</v>
       </c>
-      <c r="K108" s="7">
+      <c r="K108" s="9">
+        <v>0</v>
+      </c>
+      <c r="L108" s="7">
+        <f>IF(SUM(H108:I108)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M108" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L108" s="7"/>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N108" s="7"/>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>142</v>
       </c>
@@ -5936,13 +6699,20 @@
       <c r="J109" s="9">
         <v>0</v>
       </c>
-      <c r="K109" s="7">
+      <c r="K109" s="9">
+        <v>0</v>
+      </c>
+      <c r="L109" s="7">
+        <f>IF(SUM(H109:I109)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M109" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L109" s="7"/>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N109" s="7"/>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>143</v>
       </c>
@@ -5976,13 +6746,20 @@
       <c r="J110" s="9">
         <v>0</v>
       </c>
-      <c r="K110" s="7">
+      <c r="K110" s="9">
+        <v>0</v>
+      </c>
+      <c r="L110" s="7">
+        <f>IF(SUM(H110:I110)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M110" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L110" s="7"/>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N110" s="7"/>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>144</v>
       </c>
@@ -6011,20 +6788,27 @@
         <v>0</v>
       </c>
       <c r="I111" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J111" s="9">
-        <v>0</v>
-      </c>
-      <c r="K111" s="7">
+        <v>1</v>
+      </c>
+      <c r="K111" s="9">
+        <v>0</v>
+      </c>
+      <c r="L111" s="7">
+        <f>IF(SUM(H111:I111)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M111" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L111" s="7" t="s">
+      <c r="N111" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>145</v>
       </c>
@@ -6053,20 +6837,27 @@
         <v>0</v>
       </c>
       <c r="I112" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J112" s="9">
-        <v>0</v>
-      </c>
-      <c r="K112" s="7">
+        <v>1</v>
+      </c>
+      <c r="K112" s="9">
+        <v>0</v>
+      </c>
+      <c r="L112" s="7">
+        <f>IF(SUM(H112:I112)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M112" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L112" s="7" t="s">
+      <c r="N112" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>146</v>
       </c>
@@ -6100,13 +6891,20 @@
       <c r="J113" s="9">
         <v>0</v>
       </c>
-      <c r="K113" s="7">
+      <c r="K113" s="9">
+        <v>0</v>
+      </c>
+      <c r="L113" s="7">
+        <f>IF(SUM(H113:I113)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M113" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L113" s="7"/>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N113" s="7"/>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>147</v>
       </c>
@@ -6140,13 +6938,20 @@
       <c r="J114" s="9">
         <v>0</v>
       </c>
-      <c r="K114" s="7">
+      <c r="K114" s="9">
+        <v>0</v>
+      </c>
+      <c r="L114" s="7">
+        <f>IF(SUM(H114:I114)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M114" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L114" s="7"/>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N114" s="7"/>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>148</v>
       </c>
@@ -6180,13 +6985,20 @@
       <c r="J115" s="9">
         <v>0</v>
       </c>
-      <c r="K115" s="7">
+      <c r="K115" s="9">
+        <v>0</v>
+      </c>
+      <c r="L115" s="7">
+        <f>IF(SUM(H115:I115)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M115" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L115" s="7"/>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N115" s="7"/>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>149</v>
       </c>
@@ -6220,13 +7032,20 @@
       <c r="J116" s="9">
         <v>0</v>
       </c>
-      <c r="K116" s="7">
+      <c r="K116" s="9">
+        <v>0</v>
+      </c>
+      <c r="L116" s="7">
+        <f>IF(SUM(H116:I116)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M116" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L116" s="7"/>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N116" s="7"/>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>150</v>
       </c>
@@ -6260,13 +7079,20 @@
       <c r="J117" s="9">
         <v>0</v>
       </c>
-      <c r="K117" s="7">
+      <c r="K117" s="9">
+        <v>0</v>
+      </c>
+      <c r="L117" s="7">
+        <f>IF(SUM(H117:I117)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M117" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L117" s="7"/>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N117" s="7"/>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>151</v>
       </c>
@@ -6295,20 +7121,27 @@
         <v>0</v>
       </c>
       <c r="I118" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J118" s="9">
-        <v>1</v>
-      </c>
-      <c r="K118" s="7">
+        <v>0</v>
+      </c>
+      <c r="K118" s="9">
+        <v>0</v>
+      </c>
+      <c r="L118" s="7">
+        <f>IF(SUM(H118:I118)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M118" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L118" s="7" t="s">
+      <c r="N118" s="7" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>153</v>
       </c>
@@ -6337,20 +7170,27 @@
         <v>0</v>
       </c>
       <c r="I119" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J119" s="9">
-        <v>1</v>
-      </c>
-      <c r="K119" s="7">
+        <v>0</v>
+      </c>
+      <c r="K119" s="9">
+        <v>0</v>
+      </c>
+      <c r="L119" s="7">
+        <f>IF(SUM(H119:I119)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M119" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L119" s="7" t="s">
+      <c r="N119" s="7" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>154</v>
       </c>
@@ -6384,13 +7224,20 @@
       <c r="J120" s="9">
         <v>0</v>
       </c>
-      <c r="K120" s="7">
+      <c r="K120" s="9">
+        <v>0</v>
+      </c>
+      <c r="L120" s="7">
+        <f>IF(SUM(H120:I120)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M120" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L120" s="7"/>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N120" s="7"/>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>155</v>
       </c>
@@ -6424,13 +7271,20 @@
       <c r="J121" s="9">
         <v>0</v>
       </c>
-      <c r="K121" s="7">
+      <c r="K121" s="9">
+        <v>0</v>
+      </c>
+      <c r="L121" s="7">
+        <f>IF(SUM(H121:I121)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M121" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L121" s="7"/>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N121" s="7"/>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
         <v>156</v>
       </c>
@@ -6464,13 +7318,20 @@
       <c r="J122" s="9">
         <v>0</v>
       </c>
-      <c r="K122" s="7">
+      <c r="K122" s="9">
+        <v>0</v>
+      </c>
+      <c r="L122" s="7">
+        <f>IF(SUM(H122:I122)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M122" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L122" s="7"/>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N122" s="7"/>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
         <v>157</v>
       </c>
@@ -6504,13 +7365,20 @@
       <c r="J123" s="9">
         <v>0</v>
       </c>
-      <c r="K123" s="7">
+      <c r="K123" s="9">
+        <v>0</v>
+      </c>
+      <c r="L123" s="7">
+        <f>IF(SUM(H123:I123)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M123" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L123" s="7"/>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N123" s="7"/>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
         <v>158</v>
       </c>
@@ -6544,13 +7412,20 @@
       <c r="J124" s="9">
         <v>0</v>
       </c>
-      <c r="K124" s="7">
+      <c r="K124" s="9">
+        <v>0</v>
+      </c>
+      <c r="L124" s="7">
+        <f>IF(SUM(H124:I124)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M124" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L124" s="7"/>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N124" s="7"/>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
         <v>159</v>
       </c>
@@ -6579,20 +7454,27 @@
         <v>0</v>
       </c>
       <c r="I125" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J125" s="9">
-        <v>0</v>
-      </c>
-      <c r="K125" s="7">
+        <v>1</v>
+      </c>
+      <c r="K125" s="9">
+        <v>0</v>
+      </c>
+      <c r="L125" s="7">
+        <f>IF(SUM(H125:I125)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M125" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L125" s="7" t="s">
+      <c r="N125" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
         <v>160</v>
       </c>
@@ -6621,20 +7503,27 @@
         <v>0</v>
       </c>
       <c r="I126" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J126" s="9">
-        <v>0</v>
-      </c>
-      <c r="K126" s="7">
+        <v>1</v>
+      </c>
+      <c r="K126" s="9">
+        <v>0</v>
+      </c>
+      <c r="L126" s="7">
+        <f>IF(SUM(H126:I126)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M126" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="L126" s="7" t="s">
+      <c r="N126" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
         <v>161</v>
       </c>
@@ -6668,13 +7557,20 @@
       <c r="J127" s="9">
         <v>0</v>
       </c>
-      <c r="K127" s="7">
+      <c r="K127" s="9">
+        <v>0</v>
+      </c>
+      <c r="L127" s="7">
+        <f>IF(SUM(H127:I127)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M127" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L127" s="7"/>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N127" s="7"/>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
         <v>162</v>
       </c>
@@ -6708,13 +7604,20 @@
       <c r="J128" s="9">
         <v>0</v>
       </c>
-      <c r="K128" s="7">
+      <c r="K128" s="9">
+        <v>0</v>
+      </c>
+      <c r="L128" s="7">
+        <f>IF(SUM(H128:I128)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M128" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L128" s="7"/>
-    </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N128" s="7"/>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
         <v>163</v>
       </c>
@@ -6748,13 +7651,20 @@
       <c r="J129" s="9">
         <v>0</v>
       </c>
-      <c r="K129" s="7">
+      <c r="K129" s="9">
+        <v>0</v>
+      </c>
+      <c r="L129" s="7">
+        <f>IF(SUM(H129:I129)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M129" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L129" s="7"/>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N129" s="7"/>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
         <v>164</v>
       </c>
@@ -6788,13 +7698,20 @@
       <c r="J130" s="9">
         <v>0</v>
       </c>
-      <c r="K130" s="7">
+      <c r="K130" s="9">
+        <v>0</v>
+      </c>
+      <c r="L130" s="7">
+        <f>IF(SUM(H130:I130)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M130" s="7">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L130" s="7"/>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N130" s="7"/>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
         <v>165</v>
       </c>
@@ -6828,13 +7745,20 @@
       <c r="J131" s="9">
         <v>0</v>
       </c>
-      <c r="K131" s="7">
-        <f t="shared" ref="K131:K194" si="11">IF(SUM(H131:J131)&gt;0,0,1)</f>
-        <v>1</v>
-      </c>
-      <c r="L131" s="7"/>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K131" s="9">
+        <v>0</v>
+      </c>
+      <c r="L131" s="7">
+        <f>IF(SUM(H131:I131)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M131" s="7">
+        <f t="shared" ref="M131:M194" si="11">IF(SUM(H131:J131)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="N131" s="7"/>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
         <v>166</v>
       </c>
@@ -6863,20 +7787,27 @@
         <v>0</v>
       </c>
       <c r="I132" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J132" s="9">
-        <v>1</v>
-      </c>
-      <c r="K132" s="7">
+        <v>0</v>
+      </c>
+      <c r="K132" s="9">
+        <v>0</v>
+      </c>
+      <c r="L132" s="7">
+        <f>IF(SUM(H132:I132)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M132" s="7">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="L132" s="7" t="s">
+      <c r="N132" s="7" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
         <v>168</v>
       </c>
@@ -6905,20 +7836,27 @@
         <v>0</v>
       </c>
       <c r="I133" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J133" s="9">
-        <v>1</v>
-      </c>
-      <c r="K133" s="7">
+        <v>0</v>
+      </c>
+      <c r="K133" s="9">
+        <v>0</v>
+      </c>
+      <c r="L133" s="7">
+        <f>IF(SUM(H133:I133)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M133" s="7">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="L133" s="7" t="s">
+      <c r="N133" s="7" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
         <v>169</v>
       </c>
@@ -6952,13 +7890,20 @@
       <c r="J134" s="9">
         <v>0</v>
       </c>
-      <c r="K134" s="7">
+      <c r="K134" s="9">
+        <v>0</v>
+      </c>
+      <c r="L134" s="7">
+        <f>IF(SUM(H134:I134)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M134" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L134" s="7"/>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N134" s="7"/>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
         <v>170</v>
       </c>
@@ -6992,13 +7937,20 @@
       <c r="J135" s="9">
         <v>0</v>
       </c>
-      <c r="K135" s="7">
+      <c r="K135" s="9">
+        <v>0</v>
+      </c>
+      <c r="L135" s="7">
+        <f>IF(SUM(H135:I135)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M135" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L135" s="7"/>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N135" s="7"/>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
         <v>171</v>
       </c>
@@ -7032,13 +7984,20 @@
       <c r="J136" s="9">
         <v>0</v>
       </c>
-      <c r="K136" s="7">
+      <c r="K136" s="9">
+        <v>0</v>
+      </c>
+      <c r="L136" s="7">
+        <f>IF(SUM(H136:I136)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M136" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L136" s="7"/>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N136" s="7"/>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
         <v>172</v>
       </c>
@@ -7072,13 +8031,20 @@
       <c r="J137" s="9">
         <v>0</v>
       </c>
-      <c r="K137" s="7">
+      <c r="K137" s="9">
+        <v>0</v>
+      </c>
+      <c r="L137" s="7">
+        <f>IF(SUM(H137:I137)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M137" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L137" s="7"/>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N137" s="7"/>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
         <v>173</v>
       </c>
@@ -7112,13 +8078,20 @@
       <c r="J138" s="9">
         <v>0</v>
       </c>
-      <c r="K138" s="7">
+      <c r="K138" s="9">
+        <v>0</v>
+      </c>
+      <c r="L138" s="7">
+        <f>IF(SUM(H138:I138)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M138" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L138" s="7"/>
-    </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N138" s="7"/>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
         <v>174</v>
       </c>
@@ -7147,20 +8120,27 @@
         <v>0</v>
       </c>
       <c r="I139" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J139" s="9">
-        <v>0</v>
-      </c>
-      <c r="K139" s="7">
+        <v>1</v>
+      </c>
+      <c r="K139" s="9">
+        <v>0</v>
+      </c>
+      <c r="L139" s="7">
+        <f>IF(SUM(H139:I139)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M139" s="7">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="L139" s="7" t="s">
+      <c r="N139" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
         <v>175</v>
       </c>
@@ -7189,20 +8169,27 @@
         <v>0</v>
       </c>
       <c r="I140" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J140" s="9">
-        <v>0</v>
-      </c>
-      <c r="K140" s="7">
+        <v>1</v>
+      </c>
+      <c r="K140" s="9">
+        <v>0</v>
+      </c>
+      <c r="L140" s="7">
+        <f>IF(SUM(H140:I140)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M140" s="7">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="L140" s="7" t="s">
+      <c r="N140" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
         <v>176</v>
       </c>
@@ -7236,13 +8223,20 @@
       <c r="J141" s="9">
         <v>0</v>
       </c>
-      <c r="K141" s="7">
+      <c r="K141" s="9">
+        <v>0</v>
+      </c>
+      <c r="L141" s="7">
+        <f>IF(SUM(H141:I141)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M141" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L141" s="7"/>
-    </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N141" s="7"/>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
         <v>177</v>
       </c>
@@ -7276,13 +8270,20 @@
       <c r="J142" s="9">
         <v>0</v>
       </c>
-      <c r="K142" s="7">
+      <c r="K142" s="9">
+        <v>0</v>
+      </c>
+      <c r="L142" s="7">
+        <f>IF(SUM(H142:I142)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M142" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L142" s="7"/>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N142" s="7"/>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
         <v>178</v>
       </c>
@@ -7316,13 +8317,20 @@
       <c r="J143" s="9">
         <v>0</v>
       </c>
-      <c r="K143" s="7">
+      <c r="K143" s="9">
+        <v>0</v>
+      </c>
+      <c r="L143" s="7">
+        <f>IF(SUM(H143:I143)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M143" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L143" s="7"/>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N143" s="7"/>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
         <v>179</v>
       </c>
@@ -7356,13 +8364,20 @@
       <c r="J144" s="9">
         <v>0</v>
       </c>
-      <c r="K144" s="7">
+      <c r="K144" s="9">
+        <v>0</v>
+      </c>
+      <c r="L144" s="7">
+        <f>IF(SUM(H144:I144)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M144" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L144" s="7"/>
-    </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N144" s="7"/>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
         <v>180</v>
       </c>
@@ -7396,13 +8411,20 @@
       <c r="J145" s="9">
         <v>0</v>
       </c>
-      <c r="K145" s="7">
+      <c r="K145" s="9">
+        <v>0</v>
+      </c>
+      <c r="L145" s="7">
+        <f>IF(SUM(H145:I145)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M145" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L145" s="7"/>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N145" s="7"/>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
         <v>181</v>
       </c>
@@ -7431,20 +8453,27 @@
         <v>0</v>
       </c>
       <c r="I146" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J146" s="9">
-        <v>1</v>
-      </c>
-      <c r="K146" s="7">
+        <v>0</v>
+      </c>
+      <c r="K146" s="9">
+        <v>0</v>
+      </c>
+      <c r="L146" s="7">
+        <f>IF(SUM(H146:I146)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M146" s="7">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="L146" s="7" t="s">
+      <c r="N146" s="7" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
         <v>183</v>
       </c>
@@ -7478,13 +8507,20 @@
       <c r="J147" s="9">
         <v>0</v>
       </c>
-      <c r="K147" s="7">
+      <c r="K147" s="9">
+        <v>0</v>
+      </c>
+      <c r="L147" s="7">
+        <f>IF(SUM(H147:I147)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M147" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L147" s="7"/>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N147" s="7"/>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
         <v>184</v>
       </c>
@@ -7518,13 +8554,20 @@
       <c r="J148" s="9">
         <v>0</v>
       </c>
-      <c r="K148" s="7">
+      <c r="K148" s="9">
+        <v>0</v>
+      </c>
+      <c r="L148" s="7">
+        <f>IF(SUM(H148:I148)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M148" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L148" s="7"/>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N148" s="7"/>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
         <v>185</v>
       </c>
@@ -7558,13 +8601,20 @@
       <c r="J149" s="9">
         <v>0</v>
       </c>
-      <c r="K149" s="7">
+      <c r="K149" s="9">
+        <v>0</v>
+      </c>
+      <c r="L149" s="7">
+        <f>IF(SUM(H149:I149)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M149" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L149" s="7"/>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N149" s="7"/>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
         <v>186</v>
       </c>
@@ -7598,13 +8648,20 @@
       <c r="J150" s="9">
         <v>0</v>
       </c>
-      <c r="K150" s="7">
+      <c r="K150" s="9">
+        <v>0</v>
+      </c>
+      <c r="L150" s="7">
+        <f>IF(SUM(H150:I150)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M150" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L150" s="7"/>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N150" s="7"/>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
         <v>187</v>
       </c>
@@ -7638,13 +8695,20 @@
       <c r="J151" s="9">
         <v>0</v>
       </c>
-      <c r="K151" s="7">
+      <c r="K151" s="9">
+        <v>0</v>
+      </c>
+      <c r="L151" s="7">
+        <f>IF(SUM(H151:I151)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M151" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L151" s="7"/>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N151" s="7"/>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
         <v>188</v>
       </c>
@@ -7678,13 +8742,20 @@
       <c r="J152" s="9">
         <v>0</v>
       </c>
-      <c r="K152" s="7">
+      <c r="K152" s="9">
+        <v>0</v>
+      </c>
+      <c r="L152" s="7">
+        <f>IF(SUM(H152:I152)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M152" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L152" s="7"/>
-    </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N152" s="7"/>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
         <v>189</v>
       </c>
@@ -7718,13 +8789,20 @@
       <c r="J153" s="9">
         <v>0</v>
       </c>
-      <c r="K153" s="7">
+      <c r="K153" s="9">
+        <v>0</v>
+      </c>
+      <c r="L153" s="7">
+        <f>IF(SUM(H153:I153)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M153" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L153" s="7"/>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N153" s="7"/>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
         <v>190</v>
       </c>
@@ -7758,13 +8836,20 @@
       <c r="J154" s="9">
         <v>0</v>
       </c>
-      <c r="K154" s="7">
+      <c r="K154" s="9">
+        <v>0</v>
+      </c>
+      <c r="L154" s="7">
+        <f>IF(SUM(H154:I154)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M154" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L154" s="7"/>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N154" s="7"/>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
         <v>191</v>
       </c>
@@ -7798,13 +8883,20 @@
       <c r="J155" s="9">
         <v>0</v>
       </c>
-      <c r="K155" s="7">
+      <c r="K155" s="9">
+        <v>0</v>
+      </c>
+      <c r="L155" s="7">
+        <f>IF(SUM(H155:I155)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M155" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L155" s="7"/>
-    </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N155" s="7"/>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
         <v>192</v>
       </c>
@@ -7838,13 +8930,20 @@
       <c r="J156" s="9">
         <v>0</v>
       </c>
-      <c r="K156" s="7">
+      <c r="K156" s="9">
+        <v>0</v>
+      </c>
+      <c r="L156" s="7">
+        <f>IF(SUM(H156:I156)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M156" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L156" s="7"/>
-    </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N156" s="7"/>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
         <v>193</v>
       </c>
@@ -7878,13 +8977,20 @@
       <c r="J157" s="9">
         <v>0</v>
       </c>
-      <c r="K157" s="7">
+      <c r="K157" s="9">
+        <v>0</v>
+      </c>
+      <c r="L157" s="7">
+        <f>IF(SUM(H157:I157)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M157" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L157" s="7"/>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N157" s="7"/>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
         <v>194</v>
       </c>
@@ -7918,13 +9024,20 @@
       <c r="J158" s="9">
         <v>0</v>
       </c>
-      <c r="K158" s="7">
+      <c r="K158" s="9">
+        <v>0</v>
+      </c>
+      <c r="L158" s="7">
+        <f>IF(SUM(H158:I158)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M158" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L158" s="7"/>
-    </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N158" s="7"/>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
         <v>195</v>
       </c>
@@ -7958,13 +9071,20 @@
       <c r="J159" s="9">
         <v>0</v>
       </c>
-      <c r="K159" s="7">
+      <c r="K159" s="9">
+        <v>0</v>
+      </c>
+      <c r="L159" s="7">
+        <f>IF(SUM(H159:I159)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M159" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L159" s="7"/>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N159" s="7"/>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
         <v>196</v>
       </c>
@@ -7998,13 +9118,20 @@
       <c r="J160" s="9">
         <v>0</v>
       </c>
-      <c r="K160" s="7">
+      <c r="K160" s="9">
+        <v>0</v>
+      </c>
+      <c r="L160" s="7">
+        <f>IF(SUM(H160:I160)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M160" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L160" s="7"/>
-    </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N160" s="7"/>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
         <v>197</v>
       </c>
@@ -8038,13 +9165,20 @@
       <c r="J161" s="9">
         <v>0</v>
       </c>
-      <c r="K161" s="7">
+      <c r="K161" s="9">
+        <v>0</v>
+      </c>
+      <c r="L161" s="7">
+        <f>IF(SUM(H161:I161)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M161" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L161" s="7"/>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N161" s="7"/>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
         <v>198</v>
       </c>
@@ -8078,13 +9212,20 @@
       <c r="J162" s="9">
         <v>0</v>
       </c>
-      <c r="K162" s="7">
+      <c r="K162" s="9">
+        <v>0</v>
+      </c>
+      <c r="L162" s="7">
+        <f>IF(SUM(H162:I162)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M162" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L162" s="7"/>
-    </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N162" s="7"/>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A163" s="4" t="s">
         <v>199</v>
       </c>
@@ -8118,13 +9259,20 @@
       <c r="J163" s="9">
         <v>0</v>
       </c>
-      <c r="K163" s="7">
+      <c r="K163" s="9">
+        <v>0</v>
+      </c>
+      <c r="L163" s="7">
+        <f>IF(SUM(H163:I163)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M163" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L163" s="7"/>
-    </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N163" s="7"/>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A164" s="4" t="s">
         <v>200</v>
       </c>
@@ -8158,13 +9306,20 @@
       <c r="J164" s="9">
         <v>0</v>
       </c>
-      <c r="K164" s="7">
+      <c r="K164" s="9">
+        <v>0</v>
+      </c>
+      <c r="L164" s="7">
+        <f>IF(SUM(H164:I164)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M164" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L164" s="7"/>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N164" s="7"/>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A165" s="4" t="s">
         <v>201</v>
       </c>
@@ -8198,13 +9353,20 @@
       <c r="J165" s="9">
         <v>0</v>
       </c>
-      <c r="K165" s="7">
+      <c r="K165" s="9">
+        <v>0</v>
+      </c>
+      <c r="L165" s="7">
+        <f>IF(SUM(H165:I165)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M165" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L165" s="7"/>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N165" s="7"/>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
         <v>202</v>
       </c>
@@ -8238,13 +9400,20 @@
       <c r="J166" s="9">
         <v>0</v>
       </c>
-      <c r="K166" s="7">
+      <c r="K166" s="9">
+        <v>0</v>
+      </c>
+      <c r="L166" s="7">
+        <f>IF(SUM(H166:I166)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M166" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L166" s="7"/>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N166" s="7"/>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A167" s="4" t="s">
         <v>203</v>
       </c>
@@ -8278,13 +9447,20 @@
       <c r="J167" s="9">
         <v>0</v>
       </c>
-      <c r="K167" s="7">
+      <c r="K167" s="9">
+        <v>0</v>
+      </c>
+      <c r="L167" s="7">
+        <f>IF(SUM(H167:I167)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M167" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L167" s="7"/>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N167" s="7"/>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A168" s="4" t="s">
         <v>204</v>
       </c>
@@ -8318,13 +9494,20 @@
       <c r="J168" s="9">
         <v>0</v>
       </c>
-      <c r="K168" s="7">
+      <c r="K168" s="9">
+        <v>0</v>
+      </c>
+      <c r="L168" s="7">
+        <f>IF(SUM(H168:I168)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M168" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L168" s="7"/>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N168" s="7"/>
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
         <v>205</v>
       </c>
@@ -8358,13 +9541,20 @@
       <c r="J169" s="9">
         <v>0</v>
       </c>
-      <c r="K169" s="7">
+      <c r="K169" s="9">
+        <v>0</v>
+      </c>
+      <c r="L169" s="7">
+        <f>IF(SUM(H169:I169)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M169" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L169" s="7"/>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N169" s="7"/>
+    </row>
+    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A170" s="4" t="s">
         <v>206</v>
       </c>
@@ -8398,13 +9588,20 @@
       <c r="J170" s="9">
         <v>0</v>
       </c>
-      <c r="K170" s="7">
+      <c r="K170" s="9">
+        <v>0</v>
+      </c>
+      <c r="L170" s="7">
+        <f>IF(SUM(H170:I170)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M170" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L170" s="7"/>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N170" s="7"/>
+    </row>
+    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
         <v>207</v>
       </c>
@@ -8438,13 +9635,20 @@
       <c r="J171" s="9">
         <v>0</v>
       </c>
-      <c r="K171" s="7">
+      <c r="K171" s="9">
+        <v>0</v>
+      </c>
+      <c r="L171" s="7">
+        <f>IF(SUM(H171:I171)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M171" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L171" s="7"/>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N171" s="7"/>
+    </row>
+    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A172" s="4" t="s">
         <v>208</v>
       </c>
@@ -8478,13 +9682,20 @@
       <c r="J172" s="9">
         <v>0</v>
       </c>
-      <c r="K172" s="7">
+      <c r="K172" s="9">
+        <v>0</v>
+      </c>
+      <c r="L172" s="7">
+        <f>IF(SUM(H172:I172)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M172" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L172" s="7"/>
-    </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N172" s="7"/>
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A173" s="4" t="s">
         <v>209</v>
       </c>
@@ -8518,13 +9729,20 @@
       <c r="J173" s="9">
         <v>0</v>
       </c>
-      <c r="K173" s="7">
+      <c r="K173" s="9">
+        <v>0</v>
+      </c>
+      <c r="L173" s="7">
+        <f>IF(SUM(H173:I173)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M173" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L173" s="7"/>
-    </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N173" s="7"/>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A174" s="4" t="s">
         <v>210</v>
       </c>
@@ -8558,13 +9776,20 @@
       <c r="J174" s="9">
         <v>0</v>
       </c>
-      <c r="K174" s="7">
+      <c r="K174" s="9">
+        <v>0</v>
+      </c>
+      <c r="L174" s="7">
+        <f>IF(SUM(H174:I174)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M174" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L174" s="7"/>
-    </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N174" s="7"/>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A175" s="4" t="s">
         <v>211</v>
       </c>
@@ -8598,13 +9823,20 @@
       <c r="J175" s="9">
         <v>0</v>
       </c>
-      <c r="K175" s="7">
+      <c r="K175" s="9">
+        <v>0</v>
+      </c>
+      <c r="L175" s="7">
+        <f>IF(SUM(H175:I175)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M175" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L175" s="7"/>
-    </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N175" s="7"/>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A176" s="4" t="s">
         <v>212</v>
       </c>
@@ -8638,13 +9870,20 @@
       <c r="J176" s="9">
         <v>0</v>
       </c>
-      <c r="K176" s="7">
+      <c r="K176" s="9">
+        <v>0</v>
+      </c>
+      <c r="L176" s="7">
+        <f>IF(SUM(H176:I176)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M176" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L176" s="7"/>
-    </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N176" s="7"/>
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A177" s="4" t="s">
         <v>213</v>
       </c>
@@ -8678,13 +9917,20 @@
       <c r="J177" s="9">
         <v>0</v>
       </c>
-      <c r="K177" s="7">
+      <c r="K177" s="9">
+        <v>0</v>
+      </c>
+      <c r="L177" s="7">
+        <f>IF(SUM(H177:I177)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M177" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L177" s="7"/>
-    </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N177" s="7"/>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A178" s="4" t="s">
         <v>214</v>
       </c>
@@ -8718,13 +9964,20 @@
       <c r="J178" s="9">
         <v>0</v>
       </c>
-      <c r="K178" s="7">
+      <c r="K178" s="9">
+        <v>0</v>
+      </c>
+      <c r="L178" s="7">
+        <f>IF(SUM(H178:I178)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M178" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L178" s="7"/>
-    </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N178" s="7"/>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A179" s="4" t="s">
         <v>215</v>
       </c>
@@ -8758,13 +10011,20 @@
       <c r="J179" s="9">
         <v>0</v>
       </c>
-      <c r="K179" s="7">
+      <c r="K179" s="9">
+        <v>0</v>
+      </c>
+      <c r="L179" s="7">
+        <f>IF(SUM(H179:I179)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M179" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L179" s="7"/>
-    </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N179" s="7"/>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A180" s="4" t="s">
         <v>216</v>
       </c>
@@ -8798,13 +10058,20 @@
       <c r="J180" s="9">
         <v>0</v>
       </c>
-      <c r="K180" s="7">
+      <c r="K180" s="9">
+        <v>0</v>
+      </c>
+      <c r="L180" s="7">
+        <f>IF(SUM(H180:I180)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M180" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L180" s="7"/>
-    </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N180" s="7"/>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A181" s="4" t="s">
         <v>217</v>
       </c>
@@ -8838,13 +10105,20 @@
       <c r="J181" s="9">
         <v>0</v>
       </c>
-      <c r="K181" s="7">
+      <c r="K181" s="9">
+        <v>0</v>
+      </c>
+      <c r="L181" s="7">
+        <f>IF(SUM(H181:I181)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M181" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L181" s="7"/>
-    </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N181" s="7"/>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A182" s="4" t="s">
         <v>218</v>
       </c>
@@ -8878,13 +10152,20 @@
       <c r="J182" s="9">
         <v>0</v>
       </c>
-      <c r="K182" s="7">
+      <c r="K182" s="9">
+        <v>0</v>
+      </c>
+      <c r="L182" s="7">
+        <f>IF(SUM(H182:I182)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M182" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L182" s="7"/>
-    </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N182" s="7"/>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A183" s="4" t="s">
         <v>219</v>
       </c>
@@ -8918,13 +10199,20 @@
       <c r="J183" s="9">
         <v>0</v>
       </c>
-      <c r="K183" s="7">
+      <c r="K183" s="9">
+        <v>0</v>
+      </c>
+      <c r="L183" s="7">
+        <f>IF(SUM(H183:I183)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M183" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L183" s="7"/>
-    </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N183" s="7"/>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A184" s="4" t="s">
         <v>220</v>
       </c>
@@ -8958,13 +10246,20 @@
       <c r="J184" s="9">
         <v>0</v>
       </c>
-      <c r="K184" s="7">
+      <c r="K184" s="9">
+        <v>0</v>
+      </c>
+      <c r="L184" s="7">
+        <f>IF(SUM(H184:I184)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M184" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L184" s="7"/>
-    </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N184" s="7"/>
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A185" s="4" t="s">
         <v>221</v>
       </c>
@@ -8998,13 +10293,20 @@
       <c r="J185" s="9">
         <v>0</v>
       </c>
-      <c r="K185" s="7">
+      <c r="K185" s="9">
+        <v>1</v>
+      </c>
+      <c r="L185" s="7">
+        <f>IF(SUM(H185:I185)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M185" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L185" s="7"/>
-    </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N185" s="7"/>
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A186" s="4" t="s">
         <v>222</v>
       </c>
@@ -9038,13 +10340,20 @@
       <c r="J186" s="9">
         <v>0</v>
       </c>
-      <c r="K186" s="7">
+      <c r="K186" s="9">
+        <v>1</v>
+      </c>
+      <c r="L186" s="7">
+        <f>IF(SUM(H186:I186)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M186" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L186" s="7"/>
-    </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N186" s="7"/>
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A187" s="4" t="s">
         <v>223</v>
       </c>
@@ -9078,13 +10387,20 @@
       <c r="J187" s="9">
         <v>0</v>
       </c>
-      <c r="K187" s="7">
+      <c r="K187" s="9">
+        <v>1</v>
+      </c>
+      <c r="L187" s="7">
+        <f>IF(SUM(H187:I187)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M187" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L187" s="7"/>
-    </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N187" s="7"/>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A188" s="4" t="s">
         <v>224</v>
       </c>
@@ -9118,13 +10434,20 @@
       <c r="J188" s="9">
         <v>0</v>
       </c>
-      <c r="K188" s="7">
+      <c r="K188" s="9">
+        <v>1</v>
+      </c>
+      <c r="L188" s="7">
+        <f>IF(SUM(H188:I188)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M188" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L188" s="7"/>
-    </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N188" s="7"/>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A189" s="4" t="s">
         <v>225</v>
       </c>
@@ -9158,13 +10481,20 @@
       <c r="J189" s="9">
         <v>0</v>
       </c>
-      <c r="K189" s="7">
+      <c r="K189" s="9">
+        <v>1</v>
+      </c>
+      <c r="L189" s="7">
+        <f>IF(SUM(H189:I189)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M189" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L189" s="7"/>
-    </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N189" s="7"/>
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A190" s="4" t="s">
         <v>226</v>
       </c>
@@ -9198,13 +10528,20 @@
       <c r="J190" s="9">
         <v>0</v>
       </c>
-      <c r="K190" s="7">
+      <c r="K190" s="9">
+        <v>1</v>
+      </c>
+      <c r="L190" s="7">
+        <f>IF(SUM(H190:I190)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M190" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L190" s="7"/>
-    </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N190" s="7"/>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A191" s="4" t="s">
         <v>227</v>
       </c>
@@ -9238,13 +10575,20 @@
       <c r="J191" s="9">
         <v>0</v>
       </c>
-      <c r="K191" s="7">
+      <c r="K191" s="9">
+        <v>1</v>
+      </c>
+      <c r="L191" s="7">
+        <f>IF(SUM(H191:I191)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M191" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L191" s="7"/>
-    </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N191" s="7"/>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A192" s="4" t="s">
         <v>228</v>
       </c>
@@ -9278,13 +10622,20 @@
       <c r="J192" s="9">
         <v>0</v>
       </c>
-      <c r="K192" s="7">
+      <c r="K192" s="9">
+        <v>1</v>
+      </c>
+      <c r="L192" s="7">
+        <f>IF(SUM(H192:I192)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M192" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L192" s="7"/>
-    </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N192" s="7"/>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A193" s="4" t="s">
         <v>229</v>
       </c>
@@ -9318,13 +10669,20 @@
       <c r="J193" s="9">
         <v>0</v>
       </c>
-      <c r="K193" s="7">
+      <c r="K193" s="9">
+        <v>1</v>
+      </c>
+      <c r="L193" s="7">
+        <f>IF(SUM(H193:I193)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M193" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L193" s="7"/>
-    </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N193" s="7"/>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A194" s="4" t="s">
         <v>230</v>
       </c>
@@ -9358,13 +10716,20 @@
       <c r="J194" s="9">
         <v>0</v>
       </c>
-      <c r="K194" s="7">
+      <c r="K194" s="9">
+        <v>1</v>
+      </c>
+      <c r="L194" s="7">
+        <f>IF(SUM(H194:I194)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M194" s="7">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="L194" s="7"/>
-    </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N194" s="7"/>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A195" s="4" t="s">
         <v>231</v>
       </c>
@@ -9393,20 +10758,27 @@
         <v>0</v>
       </c>
       <c r="I195" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J195" s="9">
-        <v>0</v>
-      </c>
-      <c r="K195" s="7">
-        <f t="shared" ref="K195:K258" si="15">IF(SUM(H195:J195)&gt;0,0,1)</f>
-        <v>0</v>
-      </c>
-      <c r="L195" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="K195" s="9">
+        <v>1</v>
+      </c>
+      <c r="L195" s="7">
+        <f>IF(SUM(H195:I195)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M195" s="7">
+        <f t="shared" ref="M195:M258" si="15">IF(SUM(H195:J195)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="N195" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A196" s="4" t="s">
         <v>232</v>
       </c>
@@ -9435,20 +10807,27 @@
         <v>0</v>
       </c>
       <c r="I196" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J196" s="9">
-        <v>0</v>
-      </c>
-      <c r="K196" s="7">
+        <v>1</v>
+      </c>
+      <c r="K196" s="9">
+        <v>1</v>
+      </c>
+      <c r="L196" s="7">
+        <f>IF(SUM(H196:I196)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M196" s="7">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L196" s="7" t="s">
+      <c r="N196" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A197" s="4" t="s">
         <v>233</v>
       </c>
@@ -9482,13 +10861,20 @@
       <c r="J197" s="9">
         <v>0</v>
       </c>
-      <c r="K197" s="7">
+      <c r="K197" s="9">
+        <v>1</v>
+      </c>
+      <c r="L197" s="7">
+        <f>IF(SUM(H197:I197)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M197" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L197" s="7"/>
-    </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N197" s="7"/>
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A198" s="4" t="s">
         <v>234</v>
       </c>
@@ -9522,13 +10908,20 @@
       <c r="J198" s="9">
         <v>0</v>
       </c>
-      <c r="K198" s="7">
+      <c r="K198" s="9">
+        <v>1</v>
+      </c>
+      <c r="L198" s="7">
+        <f>IF(SUM(H198:I198)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M198" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L198" s="7"/>
-    </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N198" s="7"/>
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A199" s="4" t="s">
         <v>235</v>
       </c>
@@ -9562,13 +10955,20 @@
       <c r="J199" s="9">
         <v>0</v>
       </c>
-      <c r="K199" s="7">
+      <c r="K199" s="9">
+        <v>1</v>
+      </c>
+      <c r="L199" s="7">
+        <f>IF(SUM(H199:I199)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M199" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L199" s="7"/>
-    </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N199" s="7"/>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A200" s="4" t="s">
         <v>236</v>
       </c>
@@ -9602,13 +11002,20 @@
       <c r="J200" s="9">
         <v>0</v>
       </c>
-      <c r="K200" s="7">
+      <c r="K200" s="9">
+        <v>1</v>
+      </c>
+      <c r="L200" s="7">
+        <f>IF(SUM(H200:I200)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M200" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L200" s="7"/>
-    </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N200" s="7"/>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A201" s="4" t="s">
         <v>237</v>
       </c>
@@ -9642,13 +11049,20 @@
       <c r="J201" s="9">
         <v>0</v>
       </c>
-      <c r="K201" s="7">
+      <c r="K201" s="9">
+        <v>1</v>
+      </c>
+      <c r="L201" s="7">
+        <f>IF(SUM(H201:I201)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M201" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L201" s="7"/>
-    </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N201" s="7"/>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A202" s="4" t="s">
         <v>238</v>
       </c>
@@ -9677,20 +11091,27 @@
         <v>0</v>
       </c>
       <c r="I202" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J202" s="9">
-        <v>1</v>
-      </c>
-      <c r="K202" s="7">
+        <v>0</v>
+      </c>
+      <c r="K202" s="9">
+        <v>1</v>
+      </c>
+      <c r="L202" s="7">
+        <f>IF(SUM(H202:I202)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M202" s="7">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L202" s="7" t="s">
+      <c r="N202" s="7" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A203" s="4" t="s">
         <v>240</v>
       </c>
@@ -9724,13 +11145,20 @@
       <c r="J203" s="9">
         <v>0</v>
       </c>
-      <c r="K203" s="7">
+      <c r="K203" s="9">
+        <v>1</v>
+      </c>
+      <c r="L203" s="7">
+        <f>IF(SUM(H203:I203)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M203" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L203" s="7"/>
-    </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N203" s="7"/>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A204" s="4" t="s">
         <v>241</v>
       </c>
@@ -9764,13 +11192,20 @@
       <c r="J204" s="9">
         <v>0</v>
       </c>
-      <c r="K204" s="7">
+      <c r="K204" s="9">
+        <v>1</v>
+      </c>
+      <c r="L204" s="7">
+        <f>IF(SUM(H204:I204)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M204" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L204" s="7"/>
-    </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N204" s="7"/>
+    </row>
+    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A205" s="4" t="s">
         <v>242</v>
       </c>
@@ -9804,13 +11239,20 @@
       <c r="J205" s="9">
         <v>0</v>
       </c>
-      <c r="K205" s="7">
+      <c r="K205" s="9">
+        <v>1</v>
+      </c>
+      <c r="L205" s="7">
+        <f>IF(SUM(H205:I205)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M205" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L205" s="7"/>
-    </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N205" s="7"/>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A206" s="4" t="s">
         <v>243</v>
       </c>
@@ -9844,13 +11286,20 @@
       <c r="J206" s="9">
         <v>0</v>
       </c>
-      <c r="K206" s="7">
+      <c r="K206" s="9">
+        <v>1</v>
+      </c>
+      <c r="L206" s="7">
+        <f>IF(SUM(H206:I206)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M206" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L206" s="7"/>
-    </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N206" s="7"/>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A207" s="4" t="s">
         <v>244</v>
       </c>
@@ -9884,13 +11333,20 @@
       <c r="J207" s="9">
         <v>0</v>
       </c>
-      <c r="K207" s="7">
+      <c r="K207" s="9">
+        <v>1</v>
+      </c>
+      <c r="L207" s="7">
+        <f>IF(SUM(H207:I207)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M207" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L207" s="7"/>
-    </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N207" s="7"/>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A208" s="4" t="s">
         <v>245</v>
       </c>
@@ -9924,13 +11380,20 @@
       <c r="J208" s="9">
         <v>0</v>
       </c>
-      <c r="K208" s="7">
+      <c r="K208" s="9">
+        <v>1</v>
+      </c>
+      <c r="L208" s="7">
+        <f>IF(SUM(H208:I208)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M208" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L208" s="7"/>
-    </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N208" s="7"/>
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A209" s="4" t="s">
         <v>246</v>
       </c>
@@ -9959,20 +11422,27 @@
         <v>0</v>
       </c>
       <c r="I209" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J209" s="9">
-        <v>0</v>
-      </c>
-      <c r="K209" s="7">
+        <v>1</v>
+      </c>
+      <c r="K209" s="9">
+        <v>1</v>
+      </c>
+      <c r="L209" s="7">
+        <f>IF(SUM(H209:I209)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M209" s="7">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L209" s="7" t="s">
+      <c r="N209" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A210" s="4" t="s">
         <v>247</v>
       </c>
@@ -10001,20 +11471,27 @@
         <v>0</v>
       </c>
       <c r="I210" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J210" s="9">
-        <v>0</v>
-      </c>
-      <c r="K210" s="7">
+        <v>1</v>
+      </c>
+      <c r="K210" s="9">
+        <v>1</v>
+      </c>
+      <c r="L210" s="7">
+        <f>IF(SUM(H210:I210)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M210" s="7">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L210" s="7" t="s">
+      <c r="N210" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A211" s="4" t="s">
         <v>248</v>
       </c>
@@ -10048,13 +11525,20 @@
       <c r="J211" s="9">
         <v>0</v>
       </c>
-      <c r="K211" s="7">
+      <c r="K211" s="9">
+        <v>1</v>
+      </c>
+      <c r="L211" s="7">
+        <f>IF(SUM(H211:I211)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M211" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L211" s="7"/>
-    </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N211" s="7"/>
+    </row>
+    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A212" s="4" t="s">
         <v>249</v>
       </c>
@@ -10088,13 +11572,20 @@
       <c r="J212" s="9">
         <v>0</v>
       </c>
-      <c r="K212" s="7">
+      <c r="K212" s="9">
+        <v>1</v>
+      </c>
+      <c r="L212" s="7">
+        <f>IF(SUM(H212:I212)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M212" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L212" s="7"/>
-    </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N212" s="7"/>
+    </row>
+    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A213" s="4" t="s">
         <v>250</v>
       </c>
@@ -10128,13 +11619,20 @@
       <c r="J213" s="9">
         <v>0</v>
       </c>
-      <c r="K213" s="7">
+      <c r="K213" s="9">
+        <v>1</v>
+      </c>
+      <c r="L213" s="7">
+        <f>IF(SUM(H213:I213)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M213" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L213" s="7"/>
-    </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N213" s="7"/>
+    </row>
+    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A214" s="4" t="s">
         <v>251</v>
       </c>
@@ -10168,13 +11666,20 @@
       <c r="J214" s="9">
         <v>0</v>
       </c>
-      <c r="K214" s="7">
+      <c r="K214" s="9">
+        <v>1</v>
+      </c>
+      <c r="L214" s="7">
+        <f>IF(SUM(H214:I214)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M214" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L214" s="7"/>
-    </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N214" s="7"/>
+    </row>
+    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A215" s="4" t="s">
         <v>252</v>
       </c>
@@ -10208,13 +11713,20 @@
       <c r="J215" s="9">
         <v>0</v>
       </c>
-      <c r="K215" s="7">
+      <c r="K215" s="9">
+        <v>0</v>
+      </c>
+      <c r="L215" s="7">
+        <f>IF(SUM(H215:I215)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M215" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L215" s="7"/>
-    </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N215" s="7"/>
+    </row>
+    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A216" s="4" t="s">
         <v>253</v>
       </c>
@@ -10248,13 +11760,20 @@
       <c r="J216" s="9">
         <v>0</v>
       </c>
-      <c r="K216" s="7">
+      <c r="K216" s="9">
+        <v>0</v>
+      </c>
+      <c r="L216" s="7">
+        <f>IF(SUM(H216:I216)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M216" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L216" s="7"/>
-    </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N216" s="7"/>
+    </row>
+    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A217" s="4" t="s">
         <v>254</v>
       </c>
@@ -10288,13 +11807,20 @@
       <c r="J217" s="9">
         <v>0</v>
       </c>
-      <c r="K217" s="7">
+      <c r="K217" s="9">
+        <v>0</v>
+      </c>
+      <c r="L217" s="7">
+        <f>IF(SUM(H217:I217)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M217" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L217" s="7"/>
-    </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N217" s="7"/>
+    </row>
+    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A218" s="4" t="s">
         <v>255</v>
       </c>
@@ -10328,13 +11854,20 @@
       <c r="J218" s="9">
         <v>0</v>
       </c>
-      <c r="K218" s="7">
+      <c r="K218" s="9">
+        <v>0</v>
+      </c>
+      <c r="L218" s="7">
+        <f>IF(SUM(H218:I218)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M218" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L218" s="7"/>
-    </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N218" s="7"/>
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A219" s="4" t="s">
         <v>256</v>
       </c>
@@ -10368,13 +11901,20 @@
       <c r="J219" s="9">
         <v>0</v>
       </c>
-      <c r="K219" s="7">
+      <c r="K219" s="9">
+        <v>0</v>
+      </c>
+      <c r="L219" s="7">
+        <f>IF(SUM(H219:I219)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M219" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L219" s="7"/>
-    </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N219" s="7"/>
+    </row>
+    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A220" s="4" t="s">
         <v>257</v>
       </c>
@@ -10408,13 +11948,20 @@
       <c r="J220" s="9">
         <v>0</v>
       </c>
-      <c r="K220" s="7">
+      <c r="K220" s="9">
+        <v>0</v>
+      </c>
+      <c r="L220" s="7">
+        <f>IF(SUM(H220:I220)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M220" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L220" s="7"/>
-    </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N220" s="7"/>
+    </row>
+    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A221" s="4" t="s">
         <v>258</v>
       </c>
@@ -10448,13 +11995,20 @@
       <c r="J221" s="9">
         <v>0</v>
       </c>
-      <c r="K221" s="7">
+      <c r="K221" s="9">
+        <v>0</v>
+      </c>
+      <c r="L221" s="7">
+        <f>IF(SUM(H221:I221)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M221" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L221" s="7"/>
-    </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N221" s="7"/>
+    </row>
+    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A222" s="4" t="s">
         <v>259</v>
       </c>
@@ -10488,13 +12042,20 @@
       <c r="J222" s="9">
         <v>0</v>
       </c>
-      <c r="K222" s="7">
+      <c r="K222" s="9">
+        <v>0</v>
+      </c>
+      <c r="L222" s="7">
+        <f>IF(SUM(H222:I222)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M222" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L222" s="7"/>
-    </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N222" s="7"/>
+    </row>
+    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A223" s="4" t="s">
         <v>260</v>
       </c>
@@ -10528,13 +12089,20 @@
       <c r="J223" s="9">
         <v>0</v>
       </c>
-      <c r="K223" s="7">
+      <c r="K223" s="9">
+        <v>0</v>
+      </c>
+      <c r="L223" s="7">
+        <f>IF(SUM(H223:I223)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M223" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L223" s="7"/>
-    </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N223" s="7"/>
+    </row>
+    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A224" s="4" t="s">
         <v>261</v>
       </c>
@@ -10568,13 +12136,20 @@
       <c r="J224" s="9">
         <v>0</v>
       </c>
-      <c r="K224" s="7">
+      <c r="K224" s="9">
+        <v>0</v>
+      </c>
+      <c r="L224" s="7">
+        <f>IF(SUM(H224:I224)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M224" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L224" s="7"/>
-    </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N224" s="7"/>
+    </row>
+    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A225" s="4" t="s">
         <v>262</v>
       </c>
@@ -10608,13 +12183,20 @@
       <c r="J225" s="9">
         <v>0</v>
       </c>
-      <c r="K225" s="7">
+      <c r="K225" s="9">
+        <v>0</v>
+      </c>
+      <c r="L225" s="7">
+        <f>IF(SUM(H225:I225)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M225" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L225" s="7"/>
-    </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N225" s="7"/>
+    </row>
+    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A226" s="4" t="s">
         <v>263</v>
       </c>
@@ -10648,13 +12230,20 @@
       <c r="J226" s="9">
         <v>0</v>
       </c>
-      <c r="K226" s="7">
+      <c r="K226" s="9">
+        <v>0</v>
+      </c>
+      <c r="L226" s="7">
+        <f>IF(SUM(H226:I226)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M226" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L226" s="7"/>
-    </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N226" s="7"/>
+    </row>
+    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A227" s="4" t="s">
         <v>264</v>
       </c>
@@ -10688,13 +12277,20 @@
       <c r="J227" s="9">
         <v>0</v>
       </c>
-      <c r="K227" s="7">
+      <c r="K227" s="9">
+        <v>0</v>
+      </c>
+      <c r="L227" s="7">
+        <f>IF(SUM(H227:I227)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M227" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L227" s="7"/>
-    </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N227" s="7"/>
+    </row>
+    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A228" s="4" t="s">
         <v>265</v>
       </c>
@@ -10728,13 +12324,20 @@
       <c r="J228" s="9">
         <v>0</v>
       </c>
-      <c r="K228" s="7">
+      <c r="K228" s="9">
+        <v>0</v>
+      </c>
+      <c r="L228" s="7">
+        <f>IF(SUM(H228:I228)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M228" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L228" s="7"/>
-    </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N228" s="7"/>
+    </row>
+    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A229" s="4" t="s">
         <v>266</v>
       </c>
@@ -10768,13 +12371,20 @@
       <c r="J229" s="9">
         <v>0</v>
       </c>
-      <c r="K229" s="7">
+      <c r="K229" s="9">
+        <v>0</v>
+      </c>
+      <c r="L229" s="7">
+        <f>IF(SUM(H229:I229)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M229" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L229" s="7"/>
-    </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N229" s="7"/>
+    </row>
+    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A230" s="4" t="s">
         <v>267</v>
       </c>
@@ -10808,15 +12418,22 @@
       <c r="J230" s="9">
         <v>0</v>
       </c>
-      <c r="K230" s="7">
+      <c r="K230" s="9">
+        <v>0</v>
+      </c>
+      <c r="L230" s="7">
+        <f>IF(SUM(H230:I230)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M230" s="7">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L230" s="7" t="s">
+      <c r="N230" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A231" s="4" t="s">
         <v>268</v>
       </c>
@@ -10850,15 +12467,22 @@
       <c r="J231" s="9">
         <v>0</v>
       </c>
-      <c r="K231" s="7">
+      <c r="K231" s="9">
+        <v>0</v>
+      </c>
+      <c r="L231" s="7">
+        <f>IF(SUM(H231:I231)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M231" s="7">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L231" s="7" t="s">
+      <c r="N231" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A232" s="4" t="s">
         <v>269</v>
       </c>
@@ -10892,15 +12516,22 @@
       <c r="J232" s="9">
         <v>0</v>
       </c>
-      <c r="K232" s="7">
+      <c r="K232" s="9">
+        <v>0</v>
+      </c>
+      <c r="L232" s="7">
+        <f>IF(SUM(H232:I232)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M232" s="7">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L232" s="7" t="s">
+      <c r="N232" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A233" s="4" t="s">
         <v>270</v>
       </c>
@@ -10934,15 +12565,22 @@
       <c r="J233" s="9">
         <v>0</v>
       </c>
-      <c r="K233" s="7">
+      <c r="K233" s="9">
+        <v>0</v>
+      </c>
+      <c r="L233" s="7">
+        <f>IF(SUM(H233:I233)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M233" s="7">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L233" s="7" t="s">
+      <c r="N233" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A234" s="4" t="s">
         <v>271</v>
       </c>
@@ -10976,15 +12614,22 @@
       <c r="J234" s="9">
         <v>0</v>
       </c>
-      <c r="K234" s="7">
+      <c r="K234" s="9">
+        <v>0</v>
+      </c>
+      <c r="L234" s="7">
+        <f>IF(SUM(H234:I234)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M234" s="7">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L234" s="7" t="s">
+      <c r="N234" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A235" s="4" t="s">
         <v>272</v>
       </c>
@@ -11018,15 +12663,22 @@
       <c r="J235" s="9">
         <v>0</v>
       </c>
-      <c r="K235" s="7">
+      <c r="K235" s="9">
+        <v>0</v>
+      </c>
+      <c r="L235" s="7">
+        <f>IF(SUM(H235:I235)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M235" s="7">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L235" s="7" t="s">
+      <c r="N235" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A236" s="4" t="s">
         <v>273</v>
       </c>
@@ -11060,15 +12712,22 @@
       <c r="J236" s="9">
         <v>0</v>
       </c>
-      <c r="K236" s="7">
+      <c r="K236" s="9">
+        <v>0</v>
+      </c>
+      <c r="L236" s="7">
+        <f>IF(SUM(H236:I236)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M236" s="7">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L236" s="7" t="s">
+      <c r="N236" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A237" s="4" t="s">
         <v>274</v>
       </c>
@@ -11102,15 +12761,22 @@
       <c r="J237" s="9">
         <v>0</v>
       </c>
-      <c r="K237" s="7">
+      <c r="K237" s="9">
+        <v>0</v>
+      </c>
+      <c r="L237" s="7">
+        <f>IF(SUM(H237:I237)&gt;0,0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="M237" s="7">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L237" s="7" t="s">
+      <c r="N237" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A238" s="4" t="s">
         <v>275</v>
       </c>
@@ -11144,13 +12810,20 @@
       <c r="J238" s="9">
         <v>0</v>
       </c>
-      <c r="K238" s="7">
+      <c r="K238" s="9">
+        <v>0</v>
+      </c>
+      <c r="L238" s="7">
+        <f>IF(SUM(H238:I238)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M238" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L238" s="7"/>
-    </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N238" s="7"/>
+    </row>
+    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A239" s="4" t="s">
         <v>276</v>
       </c>
@@ -11184,13 +12857,20 @@
       <c r="J239" s="9">
         <v>0</v>
       </c>
-      <c r="K239" s="7">
+      <c r="K239" s="9">
+        <v>0</v>
+      </c>
+      <c r="L239" s="7">
+        <f>IF(SUM(H239:I239)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M239" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L239" s="7"/>
-    </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N239" s="7"/>
+    </row>
+    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A240" s="4" t="s">
         <v>277</v>
       </c>
@@ -11224,13 +12904,20 @@
       <c r="J240" s="9">
         <v>0</v>
       </c>
-      <c r="K240" s="7">
+      <c r="K240" s="9">
+        <v>0</v>
+      </c>
+      <c r="L240" s="7">
+        <f>IF(SUM(H240:I240)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M240" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L240" s="7"/>
-    </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N240" s="7"/>
+    </row>
+    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A241" s="4" t="s">
         <v>278</v>
       </c>
@@ -11264,13 +12951,20 @@
       <c r="J241" s="9">
         <v>0</v>
       </c>
-      <c r="K241" s="7">
+      <c r="K241" s="9">
+        <v>0</v>
+      </c>
+      <c r="L241" s="7">
+        <f>IF(SUM(H241:I241)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M241" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L241" s="7"/>
-    </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N241" s="7"/>
+    </row>
+    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A242" s="4" t="s">
         <v>279</v>
       </c>
@@ -11304,13 +12998,20 @@
       <c r="J242" s="9">
         <v>0</v>
       </c>
-      <c r="K242" s="7">
+      <c r="K242" s="9">
+        <v>0</v>
+      </c>
+      <c r="L242" s="7">
+        <f>IF(SUM(H242:I242)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M242" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L242" s="7"/>
-    </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N242" s="7"/>
+    </row>
+    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A243" s="4" t="s">
         <v>280</v>
       </c>
@@ -11344,13 +13045,20 @@
       <c r="J243" s="9">
         <v>0</v>
       </c>
-      <c r="K243" s="7">
+      <c r="K243" s="9">
+        <v>0</v>
+      </c>
+      <c r="L243" s="7">
+        <f>IF(SUM(H243:I243)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M243" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L243" s="7"/>
-    </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N243" s="7"/>
+    </row>
+    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A244" s="4" t="s">
         <v>281</v>
       </c>
@@ -11384,13 +13092,20 @@
       <c r="J244" s="9">
         <v>0</v>
       </c>
-      <c r="K244" s="7">
+      <c r="K244" s="9">
+        <v>0</v>
+      </c>
+      <c r="L244" s="7">
+        <f>IF(SUM(H244:I244)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M244" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L244" s="7"/>
-    </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N244" s="7"/>
+    </row>
+    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A245" s="4" t="s">
         <v>282</v>
       </c>
@@ -11424,13 +13139,20 @@
       <c r="J245" s="9">
         <v>0</v>
       </c>
-      <c r="K245" s="7">
+      <c r="K245" s="9">
+        <v>0</v>
+      </c>
+      <c r="L245" s="7">
+        <f>IF(SUM(H245:I245)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M245" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L245" s="7"/>
-    </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N245" s="7"/>
+    </row>
+    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A246" s="4" t="s">
         <v>283</v>
       </c>
@@ -11464,13 +13186,20 @@
       <c r="J246" s="9">
         <v>0</v>
       </c>
-      <c r="K246" s="7">
+      <c r="K246" s="9">
+        <v>0</v>
+      </c>
+      <c r="L246" s="7">
+        <f>IF(SUM(H246:I246)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M246" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L246" s="7"/>
-    </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N246" s="7"/>
+    </row>
+    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A247" s="4" t="s">
         <v>284</v>
       </c>
@@ -11504,13 +13233,20 @@
       <c r="J247" s="9">
         <v>0</v>
       </c>
-      <c r="K247" s="7">
+      <c r="K247" s="9">
+        <v>0</v>
+      </c>
+      <c r="L247" s="7">
+        <f>IF(SUM(H247:I247)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M247" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L247" s="7"/>
-    </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N247" s="7"/>
+    </row>
+    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A248" s="4" t="s">
         <v>285</v>
       </c>
@@ -11544,13 +13280,20 @@
       <c r="J248" s="9">
         <v>0</v>
       </c>
-      <c r="K248" s="7">
+      <c r="K248" s="9">
+        <v>0</v>
+      </c>
+      <c r="L248" s="7">
+        <f>IF(SUM(H248:I248)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M248" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L248" s="7"/>
-    </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N248" s="7"/>
+    </row>
+    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A249" s="4" t="s">
         <v>286</v>
       </c>
@@ -11584,13 +13327,20 @@
       <c r="J249" s="9">
         <v>0</v>
       </c>
-      <c r="K249" s="7">
+      <c r="K249" s="9">
+        <v>0</v>
+      </c>
+      <c r="L249" s="7">
+        <f>IF(SUM(H249:I249)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M249" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L249" s="7"/>
-    </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N249" s="7"/>
+    </row>
+    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A250" s="4" t="s">
         <v>287</v>
       </c>
@@ -11624,13 +13374,20 @@
       <c r="J250" s="9">
         <v>0</v>
       </c>
-      <c r="K250" s="7">
+      <c r="K250" s="9">
+        <v>0</v>
+      </c>
+      <c r="L250" s="7">
+        <f>IF(SUM(H250:I250)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M250" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L250" s="7"/>
-    </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N250" s="7"/>
+    </row>
+    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A251" s="4" t="s">
         <v>288</v>
       </c>
@@ -11659,20 +13416,27 @@
         <v>0</v>
       </c>
       <c r="I251" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J251" s="9">
-        <v>0</v>
-      </c>
-      <c r="K251" s="7">
+        <v>1</v>
+      </c>
+      <c r="K251" s="9">
+        <v>0</v>
+      </c>
+      <c r="L251" s="7">
+        <f>IF(SUM(H251:I251)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M251" s="7">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L251" s="7" t="s">
+      <c r="N251" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A252" s="4" t="s">
         <v>289</v>
       </c>
@@ -11701,20 +13465,27 @@
         <v>0</v>
       </c>
       <c r="I252" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J252" s="9">
-        <v>0</v>
-      </c>
-      <c r="K252" s="7">
+        <v>1</v>
+      </c>
+      <c r="K252" s="9">
+        <v>0</v>
+      </c>
+      <c r="L252" s="7">
+        <f>IF(SUM(H252:I252)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M252" s="7">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L252" s="7" t="s">
+      <c r="N252" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A253" s="4" t="s">
         <v>290</v>
       </c>
@@ -11748,13 +13519,20 @@
       <c r="J253" s="9">
         <v>0</v>
       </c>
-      <c r="K253" s="7">
+      <c r="K253" s="9">
+        <v>0</v>
+      </c>
+      <c r="L253" s="7">
+        <f>IF(SUM(H253:I253)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M253" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L253" s="7"/>
-    </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N253" s="7"/>
+    </row>
+    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A254" s="4" t="s">
         <v>291</v>
       </c>
@@ -11788,13 +13566,20 @@
       <c r="J254" s="9">
         <v>0</v>
       </c>
-      <c r="K254" s="7">
+      <c r="K254" s="9">
+        <v>0</v>
+      </c>
+      <c r="L254" s="7">
+        <f>IF(SUM(H254:I254)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M254" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L254" s="7"/>
-    </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N254" s="7"/>
+    </row>
+    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A255" s="4" t="s">
         <v>292</v>
       </c>
@@ -11828,13 +13613,20 @@
       <c r="J255" s="9">
         <v>0</v>
       </c>
-      <c r="K255" s="7">
+      <c r="K255" s="9">
+        <v>0</v>
+      </c>
+      <c r="L255" s="7">
+        <f>IF(SUM(H255:I255)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M255" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L255" s="7"/>
-    </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N255" s="7"/>
+    </row>
+    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A256" s="4" t="s">
         <v>293</v>
       </c>
@@ -11868,13 +13660,20 @@
       <c r="J256" s="9">
         <v>0</v>
       </c>
-      <c r="K256" s="7">
+      <c r="K256" s="9">
+        <v>0</v>
+      </c>
+      <c r="L256" s="7">
+        <f>IF(SUM(H256:I256)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M256" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L256" s="7"/>
-    </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N256" s="7"/>
+    </row>
+    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A257" s="4" t="s">
         <v>294</v>
       </c>
@@ -11908,13 +13707,20 @@
       <c r="J257" s="9">
         <v>0</v>
       </c>
-      <c r="K257" s="7">
+      <c r="K257" s="9">
+        <v>0</v>
+      </c>
+      <c r="L257" s="7">
+        <f>IF(SUM(H257:I257)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M257" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L257" s="7"/>
-    </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N257" s="7"/>
+    </row>
+    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A258" s="4" t="s">
         <v>295</v>
       </c>
@@ -11948,13 +13754,20 @@
       <c r="J258" s="9">
         <v>0</v>
       </c>
-      <c r="K258" s="7">
+      <c r="K258" s="9">
+        <v>0</v>
+      </c>
+      <c r="L258" s="7">
+        <f>IF(SUM(H258:I258)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M258" s="7">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L258" s="7"/>
-    </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N258" s="7"/>
+    </row>
+    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A259" s="4" t="s">
         <v>296</v>
       </c>
@@ -11988,13 +13801,20 @@
       <c r="J259" s="9">
         <v>0</v>
       </c>
-      <c r="K259" s="7">
-        <f t="shared" ref="K259:K308" si="19">IF(SUM(H259:J259)&gt;0,0,1)</f>
-        <v>1</v>
-      </c>
-      <c r="L259" s="7"/>
-    </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K259" s="9">
+        <v>0</v>
+      </c>
+      <c r="L259" s="7">
+        <f>IF(SUM(H259:I259)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M259" s="7">
+        <f t="shared" ref="M259:M308" si="19">IF(SUM(H259:J259)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="N259" s="7"/>
+    </row>
+    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A260" s="4" t="s">
         <v>297</v>
       </c>
@@ -12028,13 +13848,20 @@
       <c r="J260" s="9">
         <v>0</v>
       </c>
-      <c r="K260" s="7">
+      <c r="K260" s="9">
+        <v>0</v>
+      </c>
+      <c r="L260" s="7">
+        <f>IF(SUM(H260:I260)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M260" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L260" s="7"/>
-    </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N260" s="7"/>
+    </row>
+    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A261" s="4" t="s">
         <v>298</v>
       </c>
@@ -12068,13 +13895,20 @@
       <c r="J261" s="9">
         <v>0</v>
       </c>
-      <c r="K261" s="7">
+      <c r="K261" s="9">
+        <v>0</v>
+      </c>
+      <c r="L261" s="7">
+        <f>IF(SUM(H261:I261)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M261" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L261" s="7"/>
-    </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N261" s="7"/>
+    </row>
+    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A262" s="4" t="s">
         <v>299</v>
       </c>
@@ -12108,13 +13942,20 @@
       <c r="J262" s="9">
         <v>0</v>
       </c>
-      <c r="K262" s="7">
+      <c r="K262" s="9">
+        <v>0</v>
+      </c>
+      <c r="L262" s="7">
+        <f>IF(SUM(H262:I262)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M262" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L262" s="7"/>
-    </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N262" s="7"/>
+    </row>
+    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A263" s="4" t="s">
         <v>300</v>
       </c>
@@ -12148,13 +13989,20 @@
       <c r="J263" s="9">
         <v>0</v>
       </c>
-      <c r="K263" s="7">
+      <c r="K263" s="9">
+        <v>0</v>
+      </c>
+      <c r="L263" s="7">
+        <f>IF(SUM(H263:I263)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M263" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L263" s="7"/>
-    </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N263" s="7"/>
+    </row>
+    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A264" s="4" t="s">
         <v>301</v>
       </c>
@@ -12188,13 +14036,20 @@
       <c r="J264" s="9">
         <v>0</v>
       </c>
-      <c r="K264" s="7">
+      <c r="K264" s="9">
+        <v>0</v>
+      </c>
+      <c r="L264" s="7">
+        <f>IF(SUM(H264:I264)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M264" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L264" s="7"/>
-    </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N264" s="7"/>
+    </row>
+    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A265" s="4" t="s">
         <v>302</v>
       </c>
@@ -12223,20 +14078,27 @@
         <v>0</v>
       </c>
       <c r="I265" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J265" s="9">
-        <v>0</v>
-      </c>
-      <c r="K265" s="7">
+        <v>1</v>
+      </c>
+      <c r="K265" s="9">
+        <v>0</v>
+      </c>
+      <c r="L265" s="7">
+        <f>IF(SUM(H265:I265)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M265" s="7">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L265" s="7" t="s">
+      <c r="N265" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A266" s="4" t="s">
         <v>303</v>
       </c>
@@ -12265,20 +14127,27 @@
         <v>0</v>
       </c>
       <c r="I266" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J266" s="9">
-        <v>0</v>
-      </c>
-      <c r="K266" s="7">
+        <v>1</v>
+      </c>
+      <c r="K266" s="9">
+        <v>0</v>
+      </c>
+      <c r="L266" s="7">
+        <f>IF(SUM(H266:I266)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M266" s="7">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L266" s="7" t="s">
+      <c r="N266" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A267" s="4" t="s">
         <v>304</v>
       </c>
@@ -12312,13 +14181,20 @@
       <c r="J267" s="9">
         <v>0</v>
       </c>
-      <c r="K267" s="7">
+      <c r="K267" s="9">
+        <v>0</v>
+      </c>
+      <c r="L267" s="7">
+        <f>IF(SUM(H267:I267)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M267" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L267" s="7"/>
-    </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N267" s="7"/>
+    </row>
+    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A268" s="4" t="s">
         <v>305</v>
       </c>
@@ -12352,13 +14228,20 @@
       <c r="J268" s="9">
         <v>0</v>
       </c>
-      <c r="K268" s="7">
+      <c r="K268" s="9">
+        <v>0</v>
+      </c>
+      <c r="L268" s="7">
+        <f>IF(SUM(H268:I268)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M268" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L268" s="7"/>
-    </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N268" s="7"/>
+    </row>
+    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A269" s="4" t="s">
         <v>306</v>
       </c>
@@ -12392,13 +14275,20 @@
       <c r="J269" s="9">
         <v>0</v>
       </c>
-      <c r="K269" s="7">
+      <c r="K269" s="9">
+        <v>0</v>
+      </c>
+      <c r="L269" s="7">
+        <f>IF(SUM(H269:I269)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M269" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L269" s="7"/>
-    </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N269" s="7"/>
+    </row>
+    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A270" s="4" t="s">
         <v>307</v>
       </c>
@@ -12432,13 +14322,20 @@
       <c r="J270" s="9">
         <v>0</v>
       </c>
-      <c r="K270" s="7">
+      <c r="K270" s="9">
+        <v>0</v>
+      </c>
+      <c r="L270" s="7">
+        <f>IF(SUM(H270:I270)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M270" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L270" s="7"/>
-    </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N270" s="7"/>
+    </row>
+    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A271" s="4" t="s">
         <v>308</v>
       </c>
@@ -12472,13 +14369,20 @@
       <c r="J271" s="9">
         <v>0</v>
       </c>
-      <c r="K271" s="7">
+      <c r="K271" s="9">
+        <v>0</v>
+      </c>
+      <c r="L271" s="7">
+        <f>IF(SUM(H271:I271)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M271" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L271" s="7"/>
-    </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N271" s="7"/>
+    </row>
+    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A272" s="4" t="s">
         <v>309</v>
       </c>
@@ -12512,13 +14416,20 @@
       <c r="J272" s="9">
         <v>0</v>
       </c>
-      <c r="K272" s="7">
+      <c r="K272" s="9">
+        <v>0</v>
+      </c>
+      <c r="L272" s="7">
+        <f>IF(SUM(H272:I272)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M272" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L272" s="7"/>
-    </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N272" s="7"/>
+    </row>
+    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A273" s="4" t="s">
         <v>310</v>
       </c>
@@ -12552,13 +14463,20 @@
       <c r="J273" s="9">
         <v>0</v>
       </c>
-      <c r="K273" s="7">
+      <c r="K273" s="9">
+        <v>0</v>
+      </c>
+      <c r="L273" s="7">
+        <f>IF(SUM(H273:I273)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M273" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L273" s="7"/>
-    </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N273" s="7"/>
+    </row>
+    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A274" s="4" t="s">
         <v>311</v>
       </c>
@@ -12592,13 +14510,20 @@
       <c r="J274" s="9">
         <v>0</v>
       </c>
-      <c r="K274" s="7">
+      <c r="K274" s="9">
+        <v>0</v>
+      </c>
+      <c r="L274" s="7">
+        <f>IF(SUM(H274:I274)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M274" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L274" s="7"/>
-    </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N274" s="7"/>
+    </row>
+    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A275" s="4" t="s">
         <v>312</v>
       </c>
@@ -12632,13 +14557,20 @@
       <c r="J275" s="9">
         <v>0</v>
       </c>
-      <c r="K275" s="7">
+      <c r="K275" s="9">
+        <v>0</v>
+      </c>
+      <c r="L275" s="7">
+        <f>IF(SUM(H275:I275)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M275" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L275" s="7"/>
-    </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N275" s="7"/>
+    </row>
+    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A276" s="4" t="s">
         <v>313</v>
       </c>
@@ -12672,13 +14604,20 @@
       <c r="J276" s="9">
         <v>0</v>
       </c>
-      <c r="K276" s="7">
+      <c r="K276" s="9">
+        <v>0</v>
+      </c>
+      <c r="L276" s="7">
+        <f>IF(SUM(H276:I276)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M276" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L276" s="7"/>
-    </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N276" s="7"/>
+    </row>
+    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A277" s="4" t="s">
         <v>314</v>
       </c>
@@ -12712,13 +14651,20 @@
       <c r="J277" s="9">
         <v>0</v>
       </c>
-      <c r="K277" s="7">
+      <c r="K277" s="9">
+        <v>0</v>
+      </c>
+      <c r="L277" s="7">
+        <f>IF(SUM(H277:I277)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M277" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L277" s="7"/>
-    </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N277" s="7"/>
+    </row>
+    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A278" s="4" t="s">
         <v>315</v>
       </c>
@@ -12752,13 +14698,20 @@
       <c r="J278" s="9">
         <v>0</v>
       </c>
-      <c r="K278" s="7">
+      <c r="K278" s="9">
+        <v>0</v>
+      </c>
+      <c r="L278" s="7">
+        <f>IF(SUM(H278:I278)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M278" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L278" s="7"/>
-    </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N278" s="7"/>
+    </row>
+    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A279" s="4" t="s">
         <v>316</v>
       </c>
@@ -12792,13 +14745,20 @@
       <c r="J279" s="9">
         <v>0</v>
       </c>
-      <c r="K279" s="7">
+      <c r="K279" s="9">
+        <v>0</v>
+      </c>
+      <c r="L279" s="7">
+        <f>IF(SUM(H279:I279)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M279" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L279" s="7"/>
-    </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N279" s="7"/>
+    </row>
+    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A280" s="4" t="s">
         <v>317</v>
       </c>
@@ -12832,13 +14792,20 @@
       <c r="J280" s="9">
         <v>0</v>
       </c>
-      <c r="K280" s="7">
+      <c r="K280" s="9">
+        <v>0</v>
+      </c>
+      <c r="L280" s="7">
+        <f>IF(SUM(H280:I280)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M280" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L280" s="7"/>
-    </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N280" s="7"/>
+    </row>
+    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A281" s="4" t="s">
         <v>318</v>
       </c>
@@ -12872,13 +14839,20 @@
       <c r="J281" s="9">
         <v>0</v>
       </c>
-      <c r="K281" s="7">
+      <c r="K281" s="9">
+        <v>0</v>
+      </c>
+      <c r="L281" s="7">
+        <f>IF(SUM(H281:I281)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M281" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L281" s="7"/>
-    </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N281" s="7"/>
+    </row>
+    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A282" s="4" t="s">
         <v>319</v>
       </c>
@@ -12912,13 +14886,20 @@
       <c r="J282" s="9">
         <v>0</v>
       </c>
-      <c r="K282" s="7">
+      <c r="K282" s="9">
+        <v>0</v>
+      </c>
+      <c r="L282" s="7">
+        <f>IF(SUM(H282:I282)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M282" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L282" s="7"/>
-    </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N282" s="7"/>
+    </row>
+    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A283" s="4" t="s">
         <v>320</v>
       </c>
@@ -12952,13 +14933,20 @@
       <c r="J283" s="9">
         <v>0</v>
       </c>
-      <c r="K283" s="7">
+      <c r="K283" s="9">
+        <v>0</v>
+      </c>
+      <c r="L283" s="7">
+        <f>IF(SUM(H283:I283)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M283" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L283" s="7"/>
-    </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N283" s="7"/>
+    </row>
+    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A284" s="4" t="s">
         <v>321</v>
       </c>
@@ -12992,13 +14980,20 @@
       <c r="J284" s="9">
         <v>0</v>
       </c>
-      <c r="K284" s="7">
+      <c r="K284" s="9">
+        <v>0</v>
+      </c>
+      <c r="L284" s="7">
+        <f>IF(SUM(H284:I284)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M284" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L284" s="7"/>
-    </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N284" s="7"/>
+    </row>
+    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A285" s="4" t="s">
         <v>322</v>
       </c>
@@ -13032,13 +15027,20 @@
       <c r="J285" s="9">
         <v>0</v>
       </c>
-      <c r="K285" s="7">
+      <c r="K285" s="9">
+        <v>0</v>
+      </c>
+      <c r="L285" s="7">
+        <f>IF(SUM(H285:I285)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M285" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L285" s="7"/>
-    </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N285" s="7"/>
+    </row>
+    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A286" s="4" t="s">
         <v>323</v>
       </c>
@@ -13067,20 +15069,27 @@
         <v>0</v>
       </c>
       <c r="I286" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J286" s="9">
-        <v>0</v>
-      </c>
-      <c r="K286" s="7">
+        <v>1</v>
+      </c>
+      <c r="K286" s="9">
+        <v>0</v>
+      </c>
+      <c r="L286" s="7">
+        <f>IF(SUM(H286:I286)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M286" s="7">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L286" s="7" t="s">
+      <c r="N286" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A287" s="4" t="s">
         <v>324</v>
       </c>
@@ -13109,20 +15118,27 @@
         <v>0</v>
       </c>
       <c r="I287" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J287" s="9">
-        <v>0</v>
-      </c>
-      <c r="K287" s="7">
+        <v>1</v>
+      </c>
+      <c r="K287" s="9">
+        <v>0</v>
+      </c>
+      <c r="L287" s="7">
+        <f>IF(SUM(H287:I287)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M287" s="7">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L287" s="7" t="s">
+      <c r="N287" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A288" s="4" t="s">
         <v>325</v>
       </c>
@@ -13156,13 +15172,20 @@
       <c r="J288" s="9">
         <v>0</v>
       </c>
-      <c r="K288" s="7">
+      <c r="K288" s="9">
+        <v>0</v>
+      </c>
+      <c r="L288" s="7">
+        <f>IF(SUM(H288:I288)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M288" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L288" s="7"/>
-    </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N288" s="7"/>
+    </row>
+    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A289" s="4" t="s">
         <v>326</v>
       </c>
@@ -13196,13 +15219,20 @@
       <c r="J289" s="9">
         <v>0</v>
       </c>
-      <c r="K289" s="7">
+      <c r="K289" s="9">
+        <v>0</v>
+      </c>
+      <c r="L289" s="7">
+        <f>IF(SUM(H289:I289)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M289" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L289" s="7"/>
-    </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N289" s="7"/>
+    </row>
+    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A290" s="4" t="s">
         <v>327</v>
       </c>
@@ -13236,13 +15266,20 @@
       <c r="J290" s="9">
         <v>0</v>
       </c>
-      <c r="K290" s="7">
+      <c r="K290" s="9">
+        <v>0</v>
+      </c>
+      <c r="L290" s="7">
+        <f>IF(SUM(H290:I290)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M290" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L290" s="7"/>
-    </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N290" s="7"/>
+    </row>
+    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A291" s="4" t="s">
         <v>328</v>
       </c>
@@ -13276,13 +15313,20 @@
       <c r="J291" s="9">
         <v>0</v>
       </c>
-      <c r="K291" s="7">
+      <c r="K291" s="9">
+        <v>0</v>
+      </c>
+      <c r="L291" s="7">
+        <f>IF(SUM(H291:I291)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M291" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L291" s="7"/>
-    </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N291" s="7"/>
+    </row>
+    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A292" s="4" t="s">
         <v>329</v>
       </c>
@@ -13316,13 +15360,20 @@
       <c r="J292" s="9">
         <v>0</v>
       </c>
-      <c r="K292" s="7">
+      <c r="K292" s="9">
+        <v>0</v>
+      </c>
+      <c r="L292" s="7">
+        <f>IF(SUM(H292:I292)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M292" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L292" s="7"/>
-    </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N292" s="7"/>
+    </row>
+    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A293" s="4" t="s">
         <v>330</v>
       </c>
@@ -13356,13 +15407,20 @@
       <c r="J293" s="9">
         <v>0</v>
       </c>
-      <c r="K293" s="7">
+      <c r="K293" s="9">
+        <v>0</v>
+      </c>
+      <c r="L293" s="7">
+        <f>IF(SUM(H293:I293)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M293" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L293" s="7"/>
-    </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N293" s="7"/>
+    </row>
+    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A294" s="4" t="s">
         <v>331</v>
       </c>
@@ -13396,13 +15454,20 @@
       <c r="J294" s="9">
         <v>0</v>
       </c>
-      <c r="K294" s="7">
+      <c r="K294" s="9">
+        <v>0</v>
+      </c>
+      <c r="L294" s="7">
+        <f>IF(SUM(H294:I294)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M294" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L294" s="7"/>
-    </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N294" s="7"/>
+    </row>
+    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A295" s="4" t="s">
         <v>332</v>
       </c>
@@ -13436,13 +15501,20 @@
       <c r="J295" s="9">
         <v>0</v>
       </c>
-      <c r="K295" s="7">
+      <c r="K295" s="9">
+        <v>0</v>
+      </c>
+      <c r="L295" s="7">
+        <f>IF(SUM(H295:I295)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M295" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L295" s="7"/>
-    </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N295" s="7"/>
+    </row>
+    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A296" s="4" t="s">
         <v>333</v>
       </c>
@@ -13476,13 +15548,20 @@
       <c r="J296" s="9">
         <v>0</v>
       </c>
-      <c r="K296" s="7">
+      <c r="K296" s="9">
+        <v>0</v>
+      </c>
+      <c r="L296" s="7">
+        <f>IF(SUM(H296:I296)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M296" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L296" s="7"/>
-    </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N296" s="7"/>
+    </row>
+    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A297" s="4" t="s">
         <v>334</v>
       </c>
@@ -13516,13 +15595,20 @@
       <c r="J297" s="9">
         <v>0</v>
       </c>
-      <c r="K297" s="7">
+      <c r="K297" s="9">
+        <v>0</v>
+      </c>
+      <c r="L297" s="7">
+        <f>IF(SUM(H297:I297)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M297" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L297" s="7"/>
-    </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N297" s="7"/>
+    </row>
+    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A298" s="4" t="s">
         <v>335</v>
       </c>
@@ -13556,13 +15642,20 @@
       <c r="J298" s="9">
         <v>0</v>
       </c>
-      <c r="K298" s="7">
+      <c r="K298" s="9">
+        <v>0</v>
+      </c>
+      <c r="L298" s="7">
+        <f>IF(SUM(H298:I298)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M298" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L298" s="7"/>
-    </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N298" s="7"/>
+    </row>
+    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A299" s="4" t="s">
         <v>336</v>
       </c>
@@ -13596,13 +15689,20 @@
       <c r="J299" s="9">
         <v>0</v>
       </c>
-      <c r="K299" s="7">
+      <c r="K299" s="9">
+        <v>0</v>
+      </c>
+      <c r="L299" s="7">
+        <f>IF(SUM(H299:I299)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M299" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L299" s="7"/>
-    </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N299" s="7"/>
+    </row>
+    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A300" s="4" t="s">
         <v>337</v>
       </c>
@@ -13631,20 +15731,27 @@
         <v>0</v>
       </c>
       <c r="I300" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J300" s="9">
-        <v>0</v>
-      </c>
-      <c r="K300" s="7">
+        <v>1</v>
+      </c>
+      <c r="K300" s="9">
+        <v>0</v>
+      </c>
+      <c r="L300" s="7">
+        <f>IF(SUM(H300:I300)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M300" s="7">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L300" s="7" t="s">
+      <c r="N300" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A301" s="4" t="s">
         <v>338</v>
       </c>
@@ -13673,20 +15780,27 @@
         <v>0</v>
       </c>
       <c r="I301" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J301" s="9">
-        <v>0</v>
-      </c>
-      <c r="K301" s="7">
+        <v>1</v>
+      </c>
+      <c r="K301" s="9">
+        <v>0</v>
+      </c>
+      <c r="L301" s="7">
+        <f>IF(SUM(H301:I301)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M301" s="7">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L301" s="7" t="s">
+      <c r="N301" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A302" s="4" t="s">
         <v>339</v>
       </c>
@@ -13720,13 +15834,20 @@
       <c r="J302" s="9">
         <v>0</v>
       </c>
-      <c r="K302" s="7">
+      <c r="K302" s="9">
+        <v>0</v>
+      </c>
+      <c r="L302" s="7">
+        <f>IF(SUM(H302:I302)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M302" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L302" s="7"/>
-    </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N302" s="7"/>
+    </row>
+    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A303" s="4" t="s">
         <v>340</v>
       </c>
@@ -13760,13 +15881,20 @@
       <c r="J303" s="9">
         <v>0</v>
       </c>
-      <c r="K303" s="7">
+      <c r="K303" s="9">
+        <v>0</v>
+      </c>
+      <c r="L303" s="7">
+        <f>IF(SUM(H303:I303)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M303" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L303" s="7"/>
-    </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N303" s="7"/>
+    </row>
+    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A304" s="4" t="s">
         <v>341</v>
       </c>
@@ -13800,13 +15928,20 @@
       <c r="J304" s="9">
         <v>0</v>
       </c>
-      <c r="K304" s="7">
+      <c r="K304" s="9">
+        <v>0</v>
+      </c>
+      <c r="L304" s="7">
+        <f>IF(SUM(H304:I304)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M304" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L304" s="7"/>
-    </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N304" s="7"/>
+    </row>
+    <row r="305" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A305" s="4" t="s">
         <v>342</v>
       </c>
@@ -13840,13 +15975,20 @@
       <c r="J305" s="9">
         <v>0</v>
       </c>
-      <c r="K305" s="7">
+      <c r="K305" s="9">
+        <v>0</v>
+      </c>
+      <c r="L305" s="7">
+        <f>IF(SUM(H305:I305)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M305" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L305" s="7"/>
-    </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N305" s="7"/>
+    </row>
+    <row r="306" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A306" s="4" t="s">
         <v>343</v>
       </c>
@@ -13880,13 +16022,20 @@
       <c r="J306" s="9">
         <v>0</v>
       </c>
-      <c r="K306" s="7">
+      <c r="K306" s="9">
+        <v>0</v>
+      </c>
+      <c r="L306" s="7">
+        <f>IF(SUM(H306:I306)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M306" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L306" s="7"/>
-    </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N306" s="7"/>
+    </row>
+    <row r="307" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A307" s="4" t="s">
         <v>344</v>
       </c>
@@ -13920,13 +16069,20 @@
       <c r="J307" s="9">
         <v>0</v>
       </c>
-      <c r="K307" s="7">
+      <c r="K307" s="9">
+        <v>0</v>
+      </c>
+      <c r="L307" s="7">
+        <f>IF(SUM(H307:I307)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M307" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L307" s="7"/>
-    </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N307" s="7"/>
+    </row>
+    <row r="308" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A308" s="4" t="s">
         <v>345</v>
       </c>
@@ -13960,11 +16116,18 @@
       <c r="J308" s="9">
         <v>0</v>
       </c>
-      <c r="K308" s="7">
+      <c r="K308" s="9">
+        <v>0</v>
+      </c>
+      <c r="L308" s="7">
+        <f>IF(SUM(H308:I308)&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
+      <c r="M308" s="7">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L308" s="7"/>
+      <c r="N308" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
